--- a/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE1BF42-0AC0-4933-8F8F-F1FAA3E9B409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E838AEC-A10B-43B3-B487-A442F5B6605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28560" yWindow="2120" windowWidth="28700" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="검토요약" sheetId="1" r:id="rId1"/>
@@ -3438,10 +3438,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>늦은 카페인 줄이기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>저녁은 간단하게</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -3678,10 +3674,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>오늘은 굽거나 찌기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>혼자여도 상 차려 먹기</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -3711,6 +3703,14 @@
   </si>
   <si>
     <t>저녁은 쉬운 것으로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀김 대신 굽거나 찌기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>늦은 시간, 카페인 줄이기</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5425,7 +5425,7 @@
         <v>212</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1130</v>
+        <v>1198</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>213</v>
@@ -5460,7 +5460,7 @@
         <v>216</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>217</v>
@@ -5530,7 +5530,7 @@
         <v>224</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>225</v>
@@ -5565,7 +5565,7 @@
         <v>228</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>229</v>
@@ -5600,7 +5600,7 @@
         <v>234</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>235</v>
@@ -5635,7 +5635,7 @@
         <v>238</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>239</v>
@@ -5670,7 +5670,7 @@
         <v>242</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>243</v>
@@ -5705,7 +5705,7 @@
         <v>246</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>247</v>
@@ -5740,7 +5740,7 @@
         <v>251</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>252</v>
@@ -5775,7 +5775,7 @@
         <v>255</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>256</v>
@@ -5810,7 +5810,7 @@
         <v>259</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>260</v>
@@ -5880,7 +5880,7 @@
         <v>266</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>267</v>
@@ -6020,7 +6020,7 @@
         <v>281</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>282</v>
@@ -6090,7 +6090,7 @@
         <v>290</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>291</v>
@@ -6125,7 +6125,7 @@
         <v>294</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>295</v>
@@ -6160,7 +6160,7 @@
         <v>298</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>299</v>
@@ -6195,7 +6195,7 @@
         <v>302</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>303</v>
@@ -6230,7 +6230,7 @@
         <v>305</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>306</v>
@@ -6475,7 +6475,7 @@
         <v>344</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>345</v>
@@ -6650,7 +6650,7 @@
         <v>370</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>371</v>
@@ -6720,7 +6720,7 @@
         <v>377</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>378</v>
@@ -6755,7 +6755,7 @@
         <v>381</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>382</v>
@@ -6790,7 +6790,7 @@
         <v>385</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>386</v>
@@ -6825,7 +6825,7 @@
         <v>389</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>390</v>
@@ -6860,7 +6860,7 @@
         <v>393</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>394</v>
@@ -6895,7 +6895,7 @@
         <v>397</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>398</v>
@@ -7035,7 +7035,7 @@
         <v>416</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>417</v>
@@ -7070,7 +7070,7 @@
         <v>421</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>422</v>
@@ -7210,7 +7210,7 @@
         <v>438</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>439</v>
@@ -7245,7 +7245,7 @@
         <v>442</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>443</v>
@@ -7280,7 +7280,7 @@
         <v>445</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>446</v>
@@ -7420,7 +7420,7 @@
         <v>461</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>462</v>
@@ -7455,7 +7455,7 @@
         <v>465</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>466</v>
@@ -7490,7 +7490,7 @@
         <v>469</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>470</v>
@@ -7735,7 +7735,7 @@
         <v>497</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>498</v>
@@ -7805,7 +7805,7 @@
         <v>503</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>504</v>
@@ -7840,7 +7840,7 @@
         <v>507</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>508</v>
@@ -7910,7 +7910,7 @@
         <v>515</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>516</v>
@@ -8190,7 +8190,7 @@
         <v>554</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>555</v>
@@ -8295,7 +8295,7 @@
         <v>565</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>566</v>
@@ -8330,7 +8330,7 @@
         <v>569</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>570</v>
@@ -8400,7 +8400,7 @@
         <v>577</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>578</v>
@@ -8435,7 +8435,7 @@
         <v>581</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>582</v>
@@ -8505,7 +8505,7 @@
         <v>589</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>590</v>
@@ -8575,7 +8575,7 @@
         <v>597</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>598</v>
@@ -8925,7 +8925,7 @@
         <v>636</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>637</v>
@@ -9100,7 +9100,7 @@
         <v>654</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>655</v>
@@ -9310,7 +9310,7 @@
         <v>677</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>678</v>
@@ -9345,7 +9345,7 @@
         <v>680</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>681</v>
@@ -9380,7 +9380,7 @@
         <v>684</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>685</v>
@@ -9520,7 +9520,7 @@
         <v>698</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>699</v>
@@ -9625,7 +9625,7 @@
         <v>710</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>711</v>
@@ -9660,7 +9660,7 @@
         <v>713</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>714</v>
@@ -10185,7 +10185,7 @@
         <v>771</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>772</v>
@@ -10220,7 +10220,7 @@
         <v>775</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>776</v>
@@ -10465,7 +10465,7 @@
         <v>803</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>804</v>
@@ -10500,7 +10500,7 @@
         <v>807</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>808</v>
@@ -10535,7 +10535,7 @@
         <v>811</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>812</v>
@@ -11095,7 +11095,7 @@
         <v>869</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>870</v>
@@ -11130,7 +11130,7 @@
         <v>872</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>873</v>
@@ -11235,7 +11235,7 @@
         <v>884</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>885</v>
@@ -11305,7 +11305,7 @@
         <v>892</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>893</v>
@@ -11340,7 +11340,7 @@
         <v>896</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>897</v>
@@ -11410,7 +11410,7 @@
         <v>903</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>904</v>
@@ -11585,7 +11585,7 @@
         <v>921</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>922</v>
@@ -11655,7 +11655,7 @@
         <v>928</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>929</v>
@@ -11760,7 +11760,7 @@
         <v>939</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>940</v>
@@ -11865,7 +11865,7 @@
         <v>950</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>951</v>
@@ -12040,7 +12040,7 @@
         <v>970</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>971</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED47192-9C10-4466-BCC5-298F5ABDC531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17D3070-7E15-40AC-8EDE-63174D283084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="검토요약" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="1225">
   <si>
     <t>항목</t>
   </si>
@@ -743,18 +743,6 @@
   </si>
   <si>
     <t>개인 식사 계획에 맞춰 끼니를 챙겨요.</t>
-  </si>
-  <si>
-    <t>DIET-P-0043</t>
-  </si>
-  <si>
-    <t>주말에도 아침 거르지 않기</t>
-  </si>
-  <si>
-    <t>주말 아침을 지키면 주중 리듬이 무너지지 않아요.</t>
-  </si>
-  <si>
-    <t>주말에도 계획한 아침 식사를 챙겨요.</t>
   </si>
   <si>
     <t>DIET-P-0044</t>
@@ -3452,10 +3440,6 @@
   </si>
   <si>
     <t>오늘 세 끼 챙기기</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>주말에도 아침 챙기기</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -4119,14 +4103,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.58203125" customWidth="1"/>
-    <col min="2" max="2" width="38.58203125" customWidth="1"/>
-    <col min="3" max="3" width="60.58203125" customWidth="1"/>
+    <col min="1" max="1" width="18.59765625" customWidth="1"/>
+    <col min="2" max="2" width="38.59765625" customWidth="1"/>
+    <col min="3" max="3" width="60.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16">
+    <row r="1" spans="1:3" ht="15.6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4137,7 +4121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16">
+    <row r="2" spans="1:3" ht="15.6">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -4148,7 +4132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16">
+    <row r="3" spans="1:3" ht="15.6">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -4159,7 +4143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16">
+    <row r="4" spans="1:3" ht="15.6">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4170,7 +4154,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16">
+    <row r="5" spans="1:3" ht="15.6">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -4181,7 +4165,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16">
+    <row r="6" spans="1:3" ht="15.6">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -4192,7 +4176,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16">
+    <row r="7" spans="1:3" ht="15.6">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -4203,7 +4187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16">
+    <row r="8" spans="1:3" ht="15.6">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -4214,7 +4198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16">
+    <row r="9" spans="1:3" ht="15.6">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -4225,7 +4209,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16">
+    <row r="10" spans="1:3" ht="15.6">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -4236,7 +4220,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32">
+    <row r="11" spans="1:3" ht="31.2">
       <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
@@ -4244,7 +4228,7 @@
         <v>46301</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
     </row>
   </sheetData>
@@ -4255,24 +4239,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K226"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:K225"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" customWidth="1"/>
-    <col min="2" max="2" width="31.58203125" customWidth="1"/>
-    <col min="3" max="3" width="29.58203125" customWidth="1"/>
-    <col min="4" max="4" width="56.58203125" customWidth="1"/>
-    <col min="5" max="5" width="57.58203125" customWidth="1"/>
-    <col min="6" max="6" width="38.58203125" customWidth="1"/>
-    <col min="7" max="7" width="60.58203125" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" customWidth="1"/>
-    <col min="9" max="9" width="60.58203125" customWidth="1"/>
-    <col min="10" max="10" width="37.58203125" customWidth="1"/>
-    <col min="11" max="11" width="24.58203125" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" customWidth="1"/>
+    <col min="2" max="2" width="31.59765625" customWidth="1"/>
+    <col min="3" max="3" width="29.59765625" customWidth="1"/>
+    <col min="4" max="4" width="56.59765625" customWidth="1"/>
+    <col min="5" max="5" width="57.59765625" customWidth="1"/>
+    <col min="6" max="6" width="38.59765625" customWidth="1"/>
+    <col min="7" max="7" width="60.59765625" customWidth="1"/>
+    <col min="8" max="8" width="10.59765625" customWidth="1"/>
+    <col min="9" max="9" width="60.59765625" customWidth="1"/>
+    <col min="10" max="10" width="37.59765625" customWidth="1"/>
+    <col min="11" max="11" width="24.59765625" customWidth="1"/>
     <col min="12" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28" customHeight="1">
+    <row r="1" spans="1:11" ht="28.05" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
@@ -4307,7 +4291,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16">
+    <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
@@ -4315,7 +4299,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>42</v>
@@ -4342,7 +4326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16">
+    <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="4" t="s">
         <v>50</v>
       </c>
@@ -4377,7 +4361,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16">
+    <row r="4" spans="1:11" ht="15.6">
       <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
@@ -4385,7 +4369,7 @@
         <v>55</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>56</v>
@@ -4412,7 +4396,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16">
+    <row r="5" spans="1:11" ht="15.6">
       <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
@@ -4420,7 +4404,7 @@
         <v>59</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>60</v>
@@ -4447,7 +4431,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="32">
+    <row r="6" spans="1:11" ht="31.2">
       <c r="A6" s="4" t="s">
         <v>62</v>
       </c>
@@ -4455,7 +4439,7 @@
         <v>63</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>64</v>
@@ -4482,7 +4466,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="32">
+    <row r="7" spans="1:11" ht="31.2">
       <c r="A7" s="4" t="s">
         <v>68</v>
       </c>
@@ -4490,7 +4474,7 @@
         <v>69</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>70</v>
@@ -4517,7 +4501,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="32">
+    <row r="8" spans="1:11" ht="31.2">
       <c r="A8" s="4" t="s">
         <v>72</v>
       </c>
@@ -4552,7 +4536,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="32">
+    <row r="9" spans="1:11" ht="31.2">
       <c r="A9" s="4" t="s">
         <v>76</v>
       </c>
@@ -4560,7 +4544,7 @@
         <v>77</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>78</v>
@@ -4587,7 +4571,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16">
+    <row r="10" spans="1:11" ht="15.6">
       <c r="A10" s="4" t="s">
         <v>80</v>
       </c>
@@ -4595,7 +4579,7 @@
         <v>81</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>82</v>
@@ -4622,7 +4606,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="32">
+    <row r="11" spans="1:11" ht="31.2">
       <c r="A11" s="4" t="s">
         <v>86</v>
       </c>
@@ -4630,7 +4614,7 @@
         <v>87</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>88</v>
@@ -4657,7 +4641,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16">
+    <row r="12" spans="1:11" ht="15.6">
       <c r="A12" s="4" t="s">
         <v>92</v>
       </c>
@@ -4665,7 +4649,7 @@
         <v>93</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>94</v>
@@ -4692,7 +4676,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="32">
+    <row r="13" spans="1:11" ht="31.2">
       <c r="A13" s="4" t="s">
         <v>98</v>
       </c>
@@ -4700,7 +4684,7 @@
         <v>99</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>100</v>
@@ -4727,7 +4711,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="48">
+    <row r="14" spans="1:11" ht="46.8">
       <c r="A14" s="4" t="s">
         <v>102</v>
       </c>
@@ -4762,7 +4746,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="32">
+    <row r="15" spans="1:11" ht="31.2">
       <c r="A15" s="4" t="s">
         <v>110</v>
       </c>
@@ -4797,7 +4781,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16">
+    <row r="16" spans="1:11" ht="15.6">
       <c r="A16" s="4" t="s">
         <v>114</v>
       </c>
@@ -4832,7 +4816,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16">
+    <row r="17" spans="1:11" ht="15.6">
       <c r="A17" s="4" t="s">
         <v>118</v>
       </c>
@@ -4840,7 +4824,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>120</v>
@@ -4867,7 +4851,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16">
+    <row r="18" spans="1:11" ht="15.6">
       <c r="A18" s="4" t="s">
         <v>122</v>
       </c>
@@ -4875,7 +4859,7 @@
         <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>124</v>
@@ -4902,7 +4886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="48">
+    <row r="19" spans="1:11" ht="46.8">
       <c r="A19" s="4" t="s">
         <v>127</v>
       </c>
@@ -4937,7 +4921,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="32">
+    <row r="20" spans="1:11" ht="31.2">
       <c r="A20" s="4" t="s">
         <v>130</v>
       </c>
@@ -4972,7 +4956,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="32">
+    <row r="21" spans="1:11" ht="31.2">
       <c r="A21" s="4" t="s">
         <v>137</v>
       </c>
@@ -5007,7 +4991,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="32">
+    <row r="22" spans="1:11" ht="31.2">
       <c r="A22" s="4" t="s">
         <v>144</v>
       </c>
@@ -5042,7 +5026,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16">
+    <row r="23" spans="1:11" ht="31.2">
       <c r="A23" s="4" t="s">
         <v>151</v>
       </c>
@@ -5050,7 +5034,7 @@
         <v>152</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>153</v>
@@ -5077,7 +5061,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16">
+    <row r="24" spans="1:11" ht="31.2">
       <c r="A24" s="4" t="s">
         <v>156</v>
       </c>
@@ -5085,7 +5069,7 @@
         <v>157</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>158</v>
@@ -5112,7 +5096,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="32">
+    <row r="25" spans="1:11" ht="31.2">
       <c r="A25" s="4" t="s">
         <v>160</v>
       </c>
@@ -5147,7 +5131,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16">
+    <row r="26" spans="1:11" ht="31.2">
       <c r="A26" s="4" t="s">
         <v>165</v>
       </c>
@@ -5155,7 +5139,7 @@
         <v>166</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>167</v>
@@ -5182,7 +5166,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="32">
+    <row r="27" spans="1:11" ht="31.2">
       <c r="A27" s="4" t="s">
         <v>169</v>
       </c>
@@ -5217,7 +5201,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="32">
+    <row r="28" spans="1:11" ht="31.2">
       <c r="A28" s="4" t="s">
         <v>174</v>
       </c>
@@ -5225,7 +5209,7 @@
         <v>175</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>176</v>
@@ -5252,7 +5236,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="32">
+    <row r="29" spans="1:11" ht="31.2">
       <c r="A29" s="4" t="s">
         <v>178</v>
       </c>
@@ -5260,7 +5244,7 @@
         <v>179</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>180</v>
@@ -5287,7 +5271,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="32">
+    <row r="30" spans="1:11" ht="31.2">
       <c r="A30" s="4" t="s">
         <v>182</v>
       </c>
@@ -5295,7 +5279,7 @@
         <v>183</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>184</v>
@@ -5322,7 +5306,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="16">
+    <row r="31" spans="1:11" ht="15.6">
       <c r="A31" s="4" t="s">
         <v>186</v>
       </c>
@@ -5330,7 +5314,7 @@
         <v>187</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>188</v>
@@ -5357,7 +5341,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="32">
+    <row r="32" spans="1:11" ht="31.2">
       <c r="A32" s="4" t="s">
         <v>190</v>
       </c>
@@ -5365,7 +5349,7 @@
         <v>191</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>192</v>
@@ -5392,7 +5376,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="32">
+    <row r="33" spans="1:11" ht="31.2">
       <c r="A33" s="4" t="s">
         <v>194</v>
       </c>
@@ -5400,7 +5384,7 @@
         <v>195</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>196</v>
@@ -5427,7 +5411,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16">
+    <row r="34" spans="1:11" ht="15.6">
       <c r="A34" s="4" t="s">
         <v>200</v>
       </c>
@@ -5435,7 +5419,7 @@
         <v>201</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>202</v>
@@ -5462,7 +5446,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16">
+    <row r="35" spans="1:11" ht="15.6">
       <c r="A35" s="4" t="s">
         <v>204</v>
       </c>
@@ -5470,7 +5454,7 @@
         <v>175</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>176</v>
@@ -5497,7 +5481,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16">
+    <row r="36" spans="1:11" ht="15.6">
       <c r="A36" s="4" t="s">
         <v>206</v>
       </c>
@@ -5505,7 +5489,7 @@
         <v>207</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>208</v>
@@ -5532,7 +5516,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16">
+    <row r="37" spans="1:11" ht="15.6">
       <c r="A37" s="4" t="s">
         <v>210</v>
       </c>
@@ -5540,7 +5524,7 @@
         <v>211</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>212</v>
@@ -5567,7 +5551,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16">
+    <row r="38" spans="1:11" ht="15.6">
       <c r="A38" s="4" t="s">
         <v>214</v>
       </c>
@@ -5575,7 +5559,7 @@
         <v>215</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>216</v>
@@ -5602,7 +5586,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="32">
+    <row r="39" spans="1:11" ht="31.2">
       <c r="A39" s="4" t="s">
         <v>218</v>
       </c>
@@ -5637,7 +5621,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16">
+    <row r="40" spans="1:11" ht="15.6">
       <c r="A40" s="4" t="s">
         <v>222</v>
       </c>
@@ -5645,7 +5629,7 @@
         <v>223</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>224</v>
@@ -5672,7 +5656,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="32">
+    <row r="41" spans="1:11" ht="31.2">
       <c r="A41" s="4" t="s">
         <v>226</v>
       </c>
@@ -5680,7 +5664,7 @@
         <v>227</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>228</v>
@@ -5707,7 +5691,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="16">
+    <row r="42" spans="1:11" ht="15.6">
       <c r="A42" s="4" t="s">
         <v>232</v>
       </c>
@@ -5715,7 +5699,7 @@
         <v>233</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>234</v>
@@ -5742,7 +5726,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="16">
+    <row r="43" spans="1:11" ht="15.6">
       <c r="A43" s="4" t="s">
         <v>236</v>
       </c>
@@ -5750,7 +5734,7 @@
         <v>237</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>238</v>
@@ -5777,7 +5761,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16">
+    <row r="44" spans="1:11" ht="31.2">
       <c r="A44" s="4" t="s">
         <v>240</v>
       </c>
@@ -5785,7 +5769,7 @@
         <v>241</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>242</v>
@@ -5794,10 +5778,10 @@
         <v>243</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>46</v>
@@ -5806,48 +5790,48 @@
         <v>47</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="32">
+    <row r="45" spans="1:11" ht="31.2">
       <c r="A45" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>247</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="J45" s="4" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="32">
+    <row r="46" spans="1:11" ht="31.2">
       <c r="A46" s="4" t="s">
         <v>249</v>
       </c>
@@ -5855,16 +5839,16 @@
         <v>250</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>251</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>66</v>
@@ -5873,7 +5857,7 @@
         <v>46</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>67</v>
@@ -5882,7 +5866,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="32">
+    <row r="47" spans="1:11" ht="31.2">
       <c r="A47" s="4" t="s">
         <v>253</v>
       </c>
@@ -5890,7 +5874,7 @@
         <v>254</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>255</v>
@@ -5899,7 +5883,7 @@
         <v>256</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>66</v>
@@ -5917,24 +5901,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="32">
+    <row r="48" spans="1:11" ht="31.2">
       <c r="A48" s="4" t="s">
         <v>257</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>1138</v>
+      <c r="C48" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>259</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>66</v>
@@ -5943,7 +5927,7 @@
         <v>46</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>67</v>
@@ -5952,50 +5936,50 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="32">
+    <row r="49" spans="1:11" ht="31.2">
       <c r="A49" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="C49" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>263</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>248</v>
+        <v>44</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="32">
+    <row r="50" spans="1:11" ht="31.2">
       <c r="A50" s="4" t="s">
         <v>264</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>1139</v>
+      <c r="C50" s="4" t="s">
+        <v>265</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>266</v>
@@ -6022,7 +6006,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="32">
+    <row r="51" spans="1:11" ht="15.6">
       <c r="A51" s="4" t="s">
         <v>268</v>
       </c>
@@ -6042,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>46</v>
@@ -6051,13 +6035,13 @@
         <v>47</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="16">
+    <row r="52" spans="1:11" ht="46.8">
       <c r="A52" s="4" t="s">
         <v>272</v>
       </c>
@@ -6071,83 +6055,83 @@
         <v>274</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>275</v>
+        <v>105</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15.6">
+      <c r="A53" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J52" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="48">
-      <c r="A53" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F53" s="4" t="s">
+      <c r="J53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="31.2">
+      <c r="A54" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="16">
-      <c r="A54" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>283</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>46</v>
@@ -6156,21 +6140,21 @@
         <v>47</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="32">
+    <row r="55" spans="1:11" ht="15.6">
       <c r="A55" s="4" t="s">
         <v>284</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>285</v>
+      <c r="C55" s="6" t="s">
+        <v>1136</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>286</v>
@@ -6182,7 +6166,7 @@
         <v>44</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>46</v>
@@ -6191,13 +6175,13 @@
         <v>47</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="16">
+    <row r="56" spans="1:11" ht="15.6">
       <c r="A56" s="4" t="s">
         <v>288</v>
       </c>
@@ -6205,7 +6189,7 @@
         <v>289</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>290</v>
@@ -6217,22 +6201,22 @@
         <v>44</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="16">
+    <row r="57" spans="1:11" ht="15.6">
       <c r="A57" s="4" t="s">
         <v>292</v>
       </c>
@@ -6240,7 +6224,7 @@
         <v>293</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>294</v>
@@ -6258,7 +6242,7 @@
         <v>46</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>97</v>
@@ -6267,7 +6251,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="16">
+    <row r="58" spans="1:11" ht="15.6">
       <c r="A58" s="4" t="s">
         <v>296</v>
       </c>
@@ -6275,45 +6259,45 @@
         <v>297</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>298</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="16">
+    <row r="59" spans="1:11" ht="31.2">
       <c r="A59" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="C59" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>302</v>
@@ -6322,30 +6306,30 @@
         <v>44</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="32">
+    <row r="60" spans="1:11" ht="31.2">
       <c r="A60" s="4" t="s">
         <v>303</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>1145</v>
+      <c r="C60" s="4" t="s">
+        <v>304</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>305</v>
@@ -6354,182 +6338,182 @@
         <v>306</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>47</v>
+        <v>308</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>91</v>
+        <v>309</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="32">
+    <row r="61" spans="1:11" ht="31.2">
       <c r="A61" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="32">
+    <row r="62" spans="1:11" ht="31.2">
       <c r="A62" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="H62" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>313</v>
+        <v>155</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="32">
+    <row r="63" spans="1:11" ht="31.2">
       <c r="A63" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="G63" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="32">
+    <row r="64" spans="1:11" ht="31.2">
       <c r="A64" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="32">
+    <row r="65" spans="1:11" ht="31.2">
       <c r="A65" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>148</v>
@@ -6538,7 +6522,7 @@
         <v>107</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>155</v>
@@ -6547,33 +6531,33 @@
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="16">
+    <row r="66" spans="1:11" ht="31.2">
       <c r="A66" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>1141</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>341</v>
+        <v>47</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>155</v>
@@ -6582,15 +6566,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="16">
+    <row r="67" spans="1:11" ht="31.2">
       <c r="A67" s="4" t="s">
         <v>342</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>1146</v>
+      <c r="C67" s="4" t="s">
+        <v>343</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>344</v>
@@ -6599,16 +6583,16 @@
         <v>345</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>47</v>
+        <v>347</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>155</v>
@@ -6617,24 +6601,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="32">
+    <row r="68" spans="1:11" ht="31.2">
       <c r="A68" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>148</v>
@@ -6643,7 +6627,7 @@
         <v>107</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>155</v>
@@ -6652,24 +6636,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="32">
+    <row r="69" spans="1:11" ht="31.2">
       <c r="A69" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>148</v>
@@ -6678,7 +6662,7 @@
         <v>107</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>155</v>
@@ -6687,129 +6671,129 @@
         <v>49</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="16">
+    <row r="70" spans="1:11" ht="31.2">
       <c r="A70" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>362</v>
+        <v>47</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="32">
+    <row r="71" spans="1:11" ht="31.2">
       <c r="A71" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>1142</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>366</v>
       </c>
       <c r="F71" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="31.2">
+      <c r="A72" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="B72" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H71" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J71" s="4" t="s">
+      <c r="H72" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J72" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K71" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="32">
-      <c r="A72" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="K72" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="32">
+    <row r="73" spans="1:11" ht="31.2">
       <c r="A73" s="4" t="s">
         <v>371</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>372</v>
+      <c r="C73" s="6" t="s">
+        <v>1143</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>373</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>66</v>
@@ -6818,7 +6802,7 @@
         <v>46</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>67</v>
@@ -6827,7 +6811,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="32">
+    <row r="74" spans="1:11" ht="31.2">
       <c r="A74" s="4" t="s">
         <v>375</v>
       </c>
@@ -6835,7 +6819,7 @@
         <v>376</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>377</v>
@@ -6844,7 +6828,7 @@
         <v>378</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>66</v>
@@ -6853,7 +6837,7 @@
         <v>46</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>67</v>
@@ -6862,7 +6846,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="32">
+    <row r="75" spans="1:11" ht="15.6">
       <c r="A75" s="4" t="s">
         <v>379</v>
       </c>
@@ -6870,7 +6854,7 @@
         <v>380</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>381</v>
@@ -6879,10 +6863,10 @@
         <v>382</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>367</v>
+        <v>44</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>46</v>
@@ -6891,13 +6875,13 @@
         <v>47</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="16">
+    <row r="76" spans="1:11" ht="15.6">
       <c r="A76" s="4" t="s">
         <v>383</v>
       </c>
@@ -6905,7 +6889,7 @@
         <v>384</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>385</v>
@@ -6932,7 +6916,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="16">
+    <row r="77" spans="1:11" ht="15.6">
       <c r="A77" s="4" t="s">
         <v>387</v>
       </c>
@@ -6940,7 +6924,7 @@
         <v>388</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>389</v>
@@ -6967,7 +6951,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="16">
+    <row r="78" spans="1:11" ht="15.6">
       <c r="A78" s="4" t="s">
         <v>391</v>
       </c>
@@ -6975,7 +6959,7 @@
         <v>392</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>393</v>
@@ -7002,15 +6986,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="16">
+    <row r="79" spans="1:11" ht="15.6">
       <c r="A79" s="4" t="s">
         <v>395</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>1153</v>
+      <c r="C79" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>397</v>
@@ -7022,7 +7006,7 @@
         <v>44</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>46</v>
@@ -7031,13 +7015,13 @@
         <v>47</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="16">
+    <row r="80" spans="1:11" ht="31.2">
       <c r="A80" s="4" t="s">
         <v>399</v>
       </c>
@@ -7060,10 +7044,10 @@
         <v>45</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>47</v>
+        <v>403</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>48</v>
@@ -7072,97 +7056,97 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="32">
+    <row r="81" spans="1:11" ht="31.2">
       <c r="A81" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>44</v>
+        <v>408</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="32">
+    <row r="82" spans="1:11" ht="31.2">
       <c r="A82" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>1149</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>413</v>
+        <v>126</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="32">
+    <row r="83" spans="1:11" ht="31.2">
       <c r="A83" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>418</v>
+        <v>44</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>46</v>
@@ -7171,21 +7155,21 @@
         <v>126</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>231</v>
+        <v>91</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="32">
+    <row r="84" spans="1:11" ht="31.2">
       <c r="A84" s="4" t="s">
         <v>419</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>1155</v>
+      <c r="C84" s="4" t="s">
+        <v>420</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>421</v>
@@ -7197,57 +7181,57 @@
         <v>44</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>126</v>
+        <v>423</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="32">
+    <row r="85" spans="1:11" ht="46.8">
       <c r="A85" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>426</v>
+        <v>105</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>44</v>
+        <v>427</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>427</v>
+        <v>108</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="48">
+    <row r="86" spans="1:11" ht="15.6">
       <c r="A86" s="4" t="s">
         <v>428</v>
       </c>
@@ -7261,36 +7245,36 @@
         <v>430</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>105</v>
+        <v>431</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>431</v>
+        <v>44</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="16">
+    <row r="87" spans="1:11" ht="15.6">
       <c r="A87" s="4" t="s">
         <v>432</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>433</v>
+      <c r="C87" s="6" t="s">
+        <v>1151</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>434</v>
@@ -7299,7 +7283,7 @@
         <v>435</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>45</v>
@@ -7317,7 +7301,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="16">
+    <row r="88" spans="1:11" ht="15.6">
       <c r="A88" s="4" t="s">
         <v>436</v>
       </c>
@@ -7325,16 +7309,16 @@
         <v>437</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>438</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>45</v>
@@ -7343,7 +7327,7 @@
         <v>46</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>48</v>
@@ -7352,18 +7336,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="16">
+    <row r="89" spans="1:11" ht="15.6">
       <c r="A89" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="C89" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>442</v>
@@ -7378,7 +7362,7 @@
         <v>46</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>48</v>
@@ -7387,15 +7371,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="16">
+    <row r="90" spans="1:11" ht="15.6">
       <c r="A90" s="4" t="s">
         <v>443</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>1158</v>
+      <c r="C90" s="4" t="s">
+        <v>444</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>445</v>
@@ -7404,7 +7388,7 @@
         <v>446</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>45</v>
@@ -7422,7 +7406,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="16">
+    <row r="91" spans="1:11" ht="31.2">
       <c r="A91" s="4" t="s">
         <v>447</v>
       </c>
@@ -7439,10 +7423,10 @@
         <v>450</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>46</v>
@@ -7451,13 +7435,13 @@
         <v>47</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="32">
+    <row r="92" spans="1:11" ht="31.2">
       <c r="A92" s="4" t="s">
         <v>451</v>
       </c>
@@ -7474,7 +7458,7 @@
         <v>454</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>66</v>
@@ -7492,15 +7476,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="32">
+    <row r="93" spans="1:11" ht="31.2">
       <c r="A93" s="4" t="s">
         <v>455</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>456</v>
+      <c r="C93" s="6" t="s">
+        <v>1154</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>457</v>
@@ -7509,7 +7493,7 @@
         <v>458</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>66</v>
@@ -7527,7 +7511,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="32">
+    <row r="94" spans="1:11" ht="31.2">
       <c r="A94" s="4" t="s">
         <v>459</v>
       </c>
@@ -7535,7 +7519,7 @@
         <v>460</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>461</v>
@@ -7544,10 +7528,10 @@
         <v>462</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>46</v>
@@ -7556,13 +7540,13 @@
         <v>47</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="32">
+    <row r="95" spans="1:11" ht="31.2">
       <c r="A95" s="4" t="s">
         <v>463</v>
       </c>
@@ -7570,7 +7554,7 @@
         <v>464</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>465</v>
@@ -7579,10 +7563,10 @@
         <v>466</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>46</v>
@@ -7591,21 +7575,21 @@
         <v>47</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="32">
+    <row r="96" spans="1:11" ht="15.6">
       <c r="A96" s="4" t="s">
         <v>467</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>1161</v>
+      <c r="C96" s="4" t="s">
+        <v>468</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>469</v>
@@ -7614,10 +7598,10 @@
         <v>470</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>248</v>
+        <v>44</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>46</v>
@@ -7626,13 +7610,13 @@
         <v>47</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="16">
+    <row r="97" spans="1:11" ht="15.6">
       <c r="A97" s="4" t="s">
         <v>471</v>
       </c>
@@ -7667,7 +7651,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="16">
+    <row r="98" spans="1:11" ht="15.6">
       <c r="A98" s="4" t="s">
         <v>475</v>
       </c>
@@ -7684,10 +7668,10 @@
         <v>478</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="H98" s="4" t="s">
         <v>46</v>
@@ -7696,13 +7680,13 @@
         <v>47</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="16">
+    <row r="99" spans="1:11" ht="31.2">
       <c r="A99" s="4" t="s">
         <v>479</v>
       </c>
@@ -7719,60 +7703,60 @@
         <v>482</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I99" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="15.6">
+      <c r="A100" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I100" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J99" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="32">
-      <c r="A100" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="J100" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="16">
+    <row r="101" spans="1:11" ht="46.8">
       <c r="A101" s="4" t="s">
         <v>488</v>
       </c>
@@ -7786,77 +7770,77 @@
         <v>490</v>
       </c>
       <c r="E101" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="15.6">
+      <c r="A102" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K101" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="48">
-      <c r="A102" s="4" t="s">
+      <c r="B102" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="C102" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="E102" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="F102" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="15.6">
+      <c r="A103" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="E102" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K102" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="16">
-      <c r="A103" s="4" t="s">
+      <c r="B103" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="C103" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>497</v>
-      </c>
       <c r="E103" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>44</v>
@@ -7868,7 +7852,7 @@
         <v>46</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>48</v>
@@ -7877,18 +7861,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="16">
+    <row r="104" spans="1:11" ht="15.6">
       <c r="A104" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="C104" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>500</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>500</v>
@@ -7903,7 +7887,7 @@
         <v>46</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>48</v>
@@ -7912,7 +7896,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="16">
+    <row r="105" spans="1:11" ht="15.6">
       <c r="A105" s="4" t="s">
         <v>501</v>
       </c>
@@ -7920,7 +7904,7 @@
         <v>502</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>503</v>
@@ -7932,7 +7916,7 @@
         <v>44</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>46</v>
@@ -7941,21 +7925,21 @@
         <v>47</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="16">
+    <row r="106" spans="1:11" ht="15.6">
       <c r="A106" s="4" t="s">
         <v>505</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>1164</v>
+      <c r="C106" s="4" t="s">
+        <v>506</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>507</v>
@@ -7982,15 +7966,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="16">
+    <row r="107" spans="1:11" ht="15.6">
       <c r="A107" s="4" t="s">
         <v>509</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C107" s="4" t="s">
-        <v>510</v>
+      <c r="C107" s="6" t="s">
+        <v>1160</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>511</v>
@@ -8008,7 +7992,7 @@
         <v>46</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>97</v>
@@ -8017,15 +8001,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="16">
+    <row r="108" spans="1:11" ht="31.2">
       <c r="A108" s="4" t="s">
         <v>513</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>1165</v>
+      <c r="C108" s="4" t="s">
+        <v>514</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>515</v>
@@ -8034,95 +8018,95 @@
         <v>516</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>126</v>
+        <v>517</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="32">
+    <row r="109" spans="1:11" ht="31.2">
       <c r="A109" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>324</v>
+        <v>522</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>141</v>
+        <v>523</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>143</v>
+        <v>525</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="32">
+    <row r="110" spans="1:11" ht="31.2">
       <c r="A110" s="4" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>526</v>
+        <v>320</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>527</v>
+        <v>148</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>528</v>
+        <v>47</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>529</v>
+        <v>155</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="16">
+    <row r="111" spans="1:11" ht="31.2">
       <c r="A111" s="4" t="s">
         <v>530</v>
       </c>
@@ -8139,10 +8123,10 @@
         <v>533</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>46</v>
@@ -8151,13 +8135,13 @@
         <v>47</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="32">
+    <row r="112" spans="1:11" ht="31.2">
       <c r="A112" s="4" t="s">
         <v>534</v>
       </c>
@@ -8174,112 +8158,112 @@
         <v>537</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>134</v>
+        <v>523</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>47</v>
+        <v>538</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>136</v>
+        <v>525</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="32">
+    <row r="113" spans="1:11" ht="31.2">
       <c r="A113" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="32">
+    <row r="114" spans="1:11" ht="31.2">
       <c r="A114" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>527</v>
+        <v>141</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>547</v>
+        <v>47</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>529</v>
+        <v>143</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="32">
+    <row r="115" spans="1:11" ht="31.2">
       <c r="A115" s="4" t="s">
         <v>548</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="C115" s="4" t="s">
-        <v>549</v>
+      <c r="C115" s="6" t="s">
+        <v>1161</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>550</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>141</v>
@@ -8288,7 +8272,7 @@
         <v>46</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>143</v>
@@ -8297,68 +8281,68 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="32">
+    <row r="116" spans="1:11" ht="31.2">
       <c r="A116" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="C116" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="C116" s="6" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D116" s="4" t="s">
+      <c r="E116" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="31.2">
+      <c r="A117" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J116" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="K116" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="16">
-      <c r="A117" s="4" t="s">
+      <c r="B117" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="C117" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>556</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>557</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>557</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>324</v>
+        <v>279</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>252</v>
+        <v>558</v>
       </c>
       <c r="J117" s="4" t="s">
         <v>155</v>
@@ -8367,33 +8351,33 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="32">
+    <row r="118" spans="1:11" ht="31.2">
       <c r="A118" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>1162</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>283</v>
+        <v>357</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>562</v>
+        <v>126</v>
       </c>
       <c r="J118" s="4" t="s">
         <v>155</v>
@@ -8402,7 +8386,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="16">
+    <row r="119" spans="1:11" ht="31.2">
       <c r="A119" s="4" t="s">
         <v>563</v>
       </c>
@@ -8410,7 +8394,7 @@
         <v>564</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>565</v>
@@ -8419,33 +8403,33 @@
         <v>566</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="32">
+    <row r="120" spans="1:11" ht="31.2">
       <c r="A120" s="4" t="s">
         <v>567</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>1168</v>
+      <c r="C120" s="4" t="s">
+        <v>568</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>569</v>
@@ -8454,7 +8438,7 @@
         <v>570</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>66</v>
@@ -8472,15 +8456,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="32">
+    <row r="121" spans="1:11" ht="31.2">
       <c r="A121" s="4" t="s">
         <v>571</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>572</v>
+      <c r="C121" s="6" t="s">
+        <v>1164</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>573</v>
@@ -8489,7 +8473,7 @@
         <v>574</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>66</v>
@@ -8507,7 +8491,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="32">
+    <row r="122" spans="1:11" ht="31.2">
       <c r="A122" s="4" t="s">
         <v>575</v>
       </c>
@@ -8515,16 +8499,16 @@
         <v>576</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>577</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>66</v>
@@ -8533,7 +8517,7 @@
         <v>46</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>67</v>
@@ -8542,33 +8526,33 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="32">
+    <row r="123" spans="1:11" ht="31.2">
       <c r="A123" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="C123" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>580</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>581</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>581</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>66</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>252</v>
+        <v>582</v>
       </c>
       <c r="J123" s="4" t="s">
         <v>67</v>
@@ -8577,33 +8561,33 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="32">
+    <row r="124" spans="1:11" ht="31.2">
       <c r="A124" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>1166</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>66</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>586</v>
+        <v>47</v>
       </c>
       <c r="J124" s="4" t="s">
         <v>67</v>
@@ -8612,15 +8596,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="32">
+    <row r="125" spans="1:11" ht="15.6">
       <c r="A125" s="4" t="s">
         <v>587</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>1171</v>
+      <c r="C125" s="4" t="s">
+        <v>588</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>589</v>
@@ -8629,10 +8613,10 @@
         <v>590</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>374</v>
+        <v>44</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>46</v>
@@ -8641,27 +8625,27 @@
         <v>47</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="16">
+    <row r="126" spans="1:11" ht="15.6">
       <c r="A126" s="4" t="s">
         <v>591</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="C126" s="4" t="s">
-        <v>592</v>
+      <c r="C126" s="6" t="s">
+        <v>1167</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>593</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>44</v>
@@ -8673,7 +8657,7 @@
         <v>46</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J126" s="4" t="s">
         <v>97</v>
@@ -8682,18 +8666,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="16">
+    <row r="127" spans="1:11" ht="31.2">
       <c r="A127" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="C127" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>597</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>597</v>
@@ -8705,10 +8689,10 @@
         <v>96</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>252</v>
+        <v>598</v>
       </c>
       <c r="J127" s="4" t="s">
         <v>97</v>
@@ -8717,21 +8701,21 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="32">
+    <row r="128" spans="1:11" ht="31.2">
       <c r="A128" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>44</v>
@@ -8743,7 +8727,7 @@
         <v>107</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="J128" s="4" t="s">
         <v>97</v>
@@ -8752,88 +8736,88 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="32">
+    <row r="129" spans="1:11" ht="31.2">
       <c r="A129" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="32">
+    <row r="130" spans="1:11" ht="31.2">
       <c r="A130" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="32">
+    <row r="131" spans="1:11" ht="15.6">
       <c r="A131" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E131" s="4" t="s">
         <v>616</v>
@@ -8842,36 +8826,36 @@
         <v>44</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I131" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J131" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K131" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="15.6">
+      <c r="A132" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="J131" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K131" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="16">
-      <c r="A132" s="4" t="s">
+      <c r="B132" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="C132" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="E132" s="4" t="s">
         <v>619</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>620</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>44</v>
@@ -8883,7 +8867,7 @@
         <v>46</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>48</v>
@@ -8892,21 +8876,21 @@
         <v>49</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="16">
+    <row r="133" spans="1:11" ht="15.6">
       <c r="A133" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="C133" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="E133" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>623</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>44</v>
@@ -8918,7 +8902,7 @@
         <v>46</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>48</v>
@@ -8927,21 +8911,21 @@
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="16">
+    <row r="134" spans="1:11" ht="15.6">
       <c r="A134" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="C134" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="E134" s="4" t="s">
         <v>625</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>626</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>44</v>
@@ -8953,7 +8937,7 @@
         <v>46</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>48</v>
@@ -8962,24 +8946,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="16">
+    <row r="135" spans="1:11" ht="15.6">
       <c r="A135" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="C135" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>629</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>45</v>
@@ -8988,7 +8972,7 @@
         <v>46</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J135" s="4" t="s">
         <v>48</v>
@@ -8997,15 +8981,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="16">
+    <row r="136" spans="1:11" ht="15.6">
       <c r="A136" s="4" t="s">
         <v>630</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="C136" s="4" t="s">
-        <v>631</v>
+      <c r="C136" s="6" t="s">
+        <v>1168</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>632</v>
@@ -9014,7 +8998,7 @@
         <v>633</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>45</v>
@@ -9032,112 +9016,112 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="16">
+    <row r="137" spans="1:11" ht="31.2">
       <c r="A137" s="4" t="s">
         <v>634</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>1173</v>
+      <c r="C137" s="4" t="s">
+        <v>635</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>636</v>
       </c>
       <c r="E137" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K137" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="15.6">
+      <c r="A138" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="F137" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I137" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K137" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="32">
-      <c r="A138" s="4" t="s">
+      <c r="B138" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="C138" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="E138" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="D138" s="4" t="s">
+      <c r="F138" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J138" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K138" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="31.2">
+      <c r="A139" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="E138" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J138" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K138" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="16">
-      <c r="A139" s="4" t="s">
+      <c r="B139" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="C139" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>642</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>643</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>643</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="32">
+    <row r="140" spans="1:11" ht="31.2">
       <c r="A140" s="4" t="s">
         <v>644</v>
       </c>
@@ -9154,7 +9138,7 @@
         <v>647</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>66</v>
@@ -9172,152 +9156,152 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="32">
+    <row r="141" spans="1:11" ht="15.6">
       <c r="A141" s="4" t="s">
         <v>648</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>649</v>
+      <c r="C141" s="6" t="s">
+        <v>1169</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>650</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K141" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="31.2">
+      <c r="A142" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="F141" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J141" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K141" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="16">
-      <c r="A142" s="4" t="s">
+      <c r="B142" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="C142" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="D142" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>654</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>654</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>252</v>
+        <v>655</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="32">
+    <row r="143" spans="1:11" ht="15.6">
       <c r="A143" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>658</v>
       </c>
       <c r="F143" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I143" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G143" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I143" s="1" t="s">
+      <c r="J143" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="15.6">
+      <c r="A144" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="J143" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K143" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="16">
-      <c r="A144" s="4" t="s">
+      <c r="B144" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="C144" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="E144" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="F144" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J144" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K144" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="15.6">
+      <c r="A145" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="E144" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J144" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K144" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="16">
-      <c r="A145" s="4" t="s">
+      <c r="B145" s="4" t="s">
         <v>663</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>664</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>664</v>
@@ -9326,33 +9310,33 @@
         <v>665</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="J145" s="4" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="16">
+    <row r="146" spans="1:11" ht="15.6">
       <c r="A146" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>668</v>
@@ -9373,7 +9357,7 @@
         <v>46</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>85</v>
@@ -9382,77 +9366,77 @@
         <v>49</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="16">
+    <row r="147" spans="1:11" ht="31.2">
       <c r="A147" s="4" t="s">
         <v>671</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="C147" s="4" t="s">
-        <v>672</v>
+      <c r="C147" s="6" t="s">
+        <v>1170</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="32">
+    <row r="148" spans="1:11" ht="15.6">
       <c r="A148" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="C148" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D148" s="4" t="s">
         <v>676</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>1175</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>677</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>677</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H148" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J148" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="16">
+    <row r="149" spans="1:11" ht="15.6">
       <c r="A149" s="4" t="s">
         <v>678</v>
       </c>
@@ -9460,45 +9444,45 @@
         <v>679</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>680</v>
       </c>
       <c r="E149" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J149" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K149" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="15.6">
+      <c r="A150" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="F149" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J149" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K149" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" ht="16">
-      <c r="A150" s="4" t="s">
+      <c r="B150" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="C150" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>683</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>684</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>684</v>
@@ -9513,7 +9497,7 @@
         <v>46</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>48</v>
@@ -9522,7 +9506,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="16">
+    <row r="151" spans="1:11" ht="15.6">
       <c r="A151" s="4" t="s">
         <v>685</v>
       </c>
@@ -9536,7 +9520,7 @@
         <v>687</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>44</v>
@@ -9548,7 +9532,7 @@
         <v>46</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J151" s="4" t="s">
         <v>48</v>
@@ -9557,18 +9541,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="16">
+    <row r="152" spans="1:11" ht="15.6">
       <c r="A152" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="B152" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="C152" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>690</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>691</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>691</v>
@@ -9583,7 +9567,7 @@
         <v>46</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J152" s="4" t="s">
         <v>48</v>
@@ -9592,15 +9576,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="16">
+    <row r="153" spans="1:11" ht="15.6">
       <c r="A153" s="4" t="s">
         <v>692</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="C153" s="4" t="s">
-        <v>693</v>
+      <c r="C153" s="6" t="s">
+        <v>1173</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>694</v>
@@ -9612,7 +9596,7 @@
         <v>44</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>46</v>
@@ -9621,21 +9605,21 @@
         <v>47</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="16">
+    <row r="154" spans="1:11" ht="31.2">
       <c r="A154" s="4" t="s">
         <v>696</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>1178</v>
+      <c r="C154" s="4" t="s">
+        <v>697</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>698</v>
@@ -9647,7 +9631,7 @@
         <v>44</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>46</v>
@@ -9656,13 +9640,13 @@
         <v>47</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="32">
+    <row r="155" spans="1:11" ht="31.2">
       <c r="A155" s="4" t="s">
         <v>700</v>
       </c>
@@ -9679,10 +9663,10 @@
         <v>703</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>46</v>
@@ -9691,65 +9675,65 @@
         <v>47</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="32">
+    <row r="156" spans="1:11" ht="31.2">
       <c r="A156" s="4" t="s">
         <v>704</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>705</v>
+      <c r="C156" s="6" t="s">
+        <v>1174</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E156" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J156" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K156" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="31.2">
+      <c r="A157" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="F156" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J156" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="K156" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" ht="16">
-      <c r="A157" s="4" t="s">
+      <c r="B157" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="C157" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>709</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>710</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>710</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>148</v>
@@ -9758,7 +9742,7 @@
         <v>46</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J157" s="4" t="s">
         <v>155</v>
@@ -9767,15 +9751,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="16">
+    <row r="158" spans="1:11" ht="31.2">
       <c r="A158" s="4" t="s">
         <v>711</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>1180</v>
+      <c r="C158" s="4" t="s">
+        <v>712</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>713</v>
@@ -9784,86 +9768,86 @@
         <v>714</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G158" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="J158" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="K158" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="31.2">
+      <c r="A159" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="G159" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J158" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="K158" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" ht="32">
-      <c r="A159" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>529</v>
+        <v>155</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="16">
+    <row r="160" spans="1:11" ht="31.2">
       <c r="A160" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>724</v>
+        <v>320</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>725</v>
+        <v>47</v>
       </c>
       <c r="J160" s="4" t="s">
         <v>155</v>
@@ -9872,7 +9856,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="16">
+    <row r="161" spans="1:11" ht="31.2">
       <c r="A161" s="4" t="s">
         <v>726</v>
       </c>
@@ -9886,89 +9870,89 @@
         <v>728</v>
       </c>
       <c r="E161" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J161" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="K161" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="31.2">
+      <c r="A162" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="F161" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H161" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J161" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="K161" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" ht="32">
-      <c r="A162" s="4" t="s">
+      <c r="B162" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="C162" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D162" s="4" t="s">
         <v>731</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>732</v>
       </c>
       <c r="E162" s="4" t="s">
         <v>732</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>252</v>
+        <v>733</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="32">
+    <row r="163" spans="1:11" ht="31.2">
       <c r="A163" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E163" s="4" t="s">
         <v>736</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>737</v>
+        <v>248</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>155</v>
@@ -9977,33 +9961,33 @@
         <v>49</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="16">
+    <row r="164" spans="1:11" ht="31.2">
       <c r="A164" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B164" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="C164" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E164" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="C164" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>740</v>
-      </c>
       <c r="F164" s="4" t="s">
-        <v>324</v>
+        <v>279</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>252</v>
+        <v>740</v>
       </c>
       <c r="J164" s="4" t="s">
         <v>155</v>
@@ -10012,7 +9996,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="32">
+    <row r="165" spans="1:11" ht="31.2">
       <c r="A165" s="4" t="s">
         <v>741</v>
       </c>
@@ -10023,48 +10007,48 @@
         <v>742</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>560</v>
+        <v>743</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>743</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>283</v>
+        <v>363</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I165" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J165" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="31.2">
+      <c r="A166" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="J165" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="K165" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" ht="32">
-      <c r="A166" s="4" t="s">
+      <c r="B166" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="C166" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D166" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="E166" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="D166" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>747</v>
-      </c>
       <c r="F166" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>66</v>
@@ -10073,7 +10057,7 @@
         <v>46</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J166" s="4" t="s">
         <v>67</v>
@@ -10082,24 +10066,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="32">
+    <row r="167" spans="1:11" ht="31.2">
       <c r="A167" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="B167" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="C167" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D167" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="E167" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="D167" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>750</v>
-      </c>
       <c r="F167" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>66</v>
@@ -10108,7 +10092,7 @@
         <v>46</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>67</v>
@@ -10117,24 +10101,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="32">
+    <row r="168" spans="1:11" ht="31.2">
       <c r="A168" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="B168" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="C168" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D168" s="4" t="s">
         <v>752</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>753</v>
       </c>
       <c r="E168" s="4" t="s">
         <v>753</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>66</v>
@@ -10143,7 +10127,7 @@
         <v>46</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J168" s="4" t="s">
         <v>67</v>
@@ -10152,7 +10136,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="32">
+    <row r="169" spans="1:11" ht="31.2">
       <c r="A169" s="4" t="s">
         <v>754</v>
       </c>
@@ -10169,7 +10153,7 @@
         <v>757</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>66</v>
@@ -10187,7 +10171,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="32">
+    <row r="170" spans="1:11" ht="31.2">
       <c r="A170" s="4" t="s">
         <v>758</v>
       </c>
@@ -10201,71 +10185,71 @@
         <v>760</v>
       </c>
       <c r="E170" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J170" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="K170" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" ht="15.6">
+      <c r="A171" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="F170" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H170" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I170" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J170" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K170" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" ht="32">
-      <c r="A171" s="4" t="s">
+      <c r="B171" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="C171" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>763</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>763</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>764</v>
       </c>
       <c r="E171" s="4" t="s">
         <v>764</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>199</v>
+        <v>48</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="16">
+    <row r="172" spans="1:11" ht="15.6">
       <c r="A172" s="4" t="s">
         <v>765</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="C172" s="4" t="s">
-        <v>766</v>
+      <c r="C172" s="6" t="s">
+        <v>1176</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>767</v>
@@ -10292,7 +10276,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="16">
+    <row r="173" spans="1:11" ht="15.6">
       <c r="A173" s="4" t="s">
         <v>769</v>
       </c>
@@ -10300,7 +10284,7 @@
         <v>770</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>771</v>
@@ -10327,15 +10311,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="16">
+    <row r="174" spans="1:11" ht="15.6">
       <c r="A174" s="4" t="s">
         <v>773</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="C174" s="6" t="s">
-        <v>1182</v>
+      <c r="C174" s="4" t="s">
+        <v>774</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>775</v>
@@ -10362,7 +10346,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="16">
+    <row r="175" spans="1:11" ht="31.2">
       <c r="A175" s="4" t="s">
         <v>777</v>
       </c>
@@ -10376,28 +10360,28 @@
         <v>779</v>
       </c>
       <c r="E175" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I175" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="F175" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H175" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I175" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="J175" s="4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="32">
+    <row r="176" spans="1:11" ht="31.2">
       <c r="A176" s="4" t="s">
         <v>781</v>
       </c>
@@ -10411,168 +10395,168 @@
         <v>783</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H176" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="32">
+    <row r="177" spans="1:11" ht="31.2">
       <c r="A177" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E177" s="4" t="s">
         <v>788</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I177" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="J177" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K177" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="15.6">
+      <c r="A178" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="J177" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K177" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" ht="32">
-      <c r="A178" s="4" t="s">
+      <c r="B178" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="C178" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D178" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="E178" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="D178" s="4" t="s">
-        <v>792</v>
-      </c>
-      <c r="E178" s="4" t="s">
-        <v>792</v>
-      </c>
       <c r="F178" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H178" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="16">
+    <row r="179" spans="1:11" ht="31.2">
       <c r="A179" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="B179" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="C179" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D179" s="4" t="s">
         <v>794</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>795</v>
       </c>
       <c r="E179" s="4" t="s">
         <v>795</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>248</v>
+        <v>796</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="32">
+    <row r="180" spans="1:11" ht="15.6">
       <c r="A180" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>1178</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>800</v>
+        <v>44</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>789</v>
+        <v>126</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="16">
+    <row r="181" spans="1:11" ht="15.6">
       <c r="A181" s="4" t="s">
         <v>801</v>
       </c>
@@ -10580,7 +10564,7 @@
         <v>802</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>803</v>
@@ -10607,7 +10591,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="16">
+    <row r="182" spans="1:11" ht="31.2">
       <c r="A182" s="4" t="s">
         <v>805</v>
       </c>
@@ -10615,7 +10599,7 @@
         <v>806</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>807</v>
@@ -10624,10 +10608,10 @@
         <v>808</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>46</v>
@@ -10636,21 +10620,21 @@
         <v>126</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="32">
+    <row r="183" spans="1:11" ht="31.2">
       <c r="A183" s="4" t="s">
         <v>809</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>810</v>
       </c>
-      <c r="C183" s="6" t="s">
-        <v>1185</v>
+      <c r="C183" s="4" t="s">
+        <v>810</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>811</v>
@@ -10659,25 +10643,25 @@
         <v>812</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>248</v>
+        <v>44</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="32">
+    <row r="184" spans="1:11" ht="15.6">
       <c r="A184" s="4" t="s">
         <v>813</v>
       </c>
@@ -10691,98 +10675,98 @@
         <v>815</v>
       </c>
       <c r="E184" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="J184" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K184" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" ht="31.2">
+      <c r="A185" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="F184" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H184" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I184" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J184" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="K184" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11" ht="16">
-      <c r="A185" s="4" t="s">
+      <c r="B185" s="4" t="s">
         <v>817</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="C185" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="D185" s="4" t="s">
         <v>818</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="E185" s="4" t="s">
         <v>818</v>
       </c>
-      <c r="D185" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="E185" s="4" t="s">
-        <v>819</v>
-      </c>
       <c r="F185" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="32">
+    <row r="186" spans="1:11" ht="31.2">
       <c r="A186" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="B186" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="C186" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D186" s="4" t="s">
         <v>821</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="D186" s="4" t="s">
-        <v>822</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>822</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>248</v>
+        <v>427</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="32">
+    <row r="187" spans="1:11" ht="31.2">
       <c r="A187" s="4" t="s">
         <v>823</v>
       </c>
@@ -10799,7 +10783,7 @@
         <v>826</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>431</v>
+        <v>244</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>45</v>
@@ -10808,7 +10792,7 @@
         <v>107</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="J187" s="4" t="s">
         <v>48</v>
@@ -10817,7 +10801,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="32">
+    <row r="188" spans="1:11" ht="31.2">
       <c r="A188" s="4" t="s">
         <v>827</v>
       </c>
@@ -10834,7 +10818,7 @@
         <v>830</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>45</v>
@@ -10843,7 +10827,7 @@
         <v>107</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="J188" s="4" t="s">
         <v>48</v>
@@ -10852,7 +10836,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="32">
+    <row r="189" spans="1:11" ht="31.2">
       <c r="A189" s="4" t="s">
         <v>831</v>
       </c>
@@ -10866,98 +10850,98 @@
         <v>833</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="32">
+    <row r="190" spans="1:11" ht="15.6">
       <c r="A190" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="B190" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="C190" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="D190" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="C190" s="4" t="s">
+      <c r="E190" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="D190" s="4" t="s">
-        <v>837</v>
-      </c>
-      <c r="E190" s="4" t="s">
-        <v>837</v>
-      </c>
       <c r="F190" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="H190" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="16">
+    <row r="191" spans="1:11" ht="31.2">
       <c r="A191" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="B191" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="C191" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="D191" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="C191" s="4" t="s">
-        <v>839</v>
-      </c>
-      <c r="D191" s="4" t="s">
-        <v>840</v>
-      </c>
       <c r="E191" s="4" t="s">
-        <v>840</v>
+        <v>105</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>784</v>
+        <v>840</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="32">
+    <row r="192" spans="1:11" ht="31.2">
       <c r="A192" s="4" t="s">
         <v>841</v>
       </c>
@@ -10971,10 +10955,10 @@
         <v>843</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>105</v>
+        <v>843</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>66</v>
@@ -10983,68 +10967,68 @@
         <v>107</v>
       </c>
       <c r="I192" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="J192" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K192" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" ht="31.2">
+      <c r="A193" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="J192" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K192" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" ht="32">
-      <c r="A193" s="4" t="s">
+      <c r="B193" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="C193" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="D193" s="4" t="s">
         <v>846</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>847</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>847</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>248</v>
+        <v>848</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="32">
+    <row r="194" spans="1:11" ht="31.2">
       <c r="A194" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>852</v>
+        <v>244</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>45</v>
@@ -11053,7 +11037,7 @@
         <v>107</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>48</v>
@@ -11062,7 +11046,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="32">
+    <row r="195" spans="1:11" ht="31.2">
       <c r="A195" s="4" t="s">
         <v>853</v>
       </c>
@@ -11076,28 +11060,28 @@
         <v>855</v>
       </c>
       <c r="E195" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F195" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="F195" s="4" t="s">
-        <v>248</v>
-      </c>
       <c r="G195" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>789</v>
+        <v>840</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="K195" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="32">
+    <row r="196" spans="1:11" ht="31.2">
       <c r="A196" s="4" t="s">
         <v>857</v>
       </c>
@@ -11111,10 +11095,10 @@
         <v>859</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>105</v>
+        <v>859</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>860</v>
+        <v>244</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>66</v>
@@ -11123,103 +11107,103 @@
         <v>107</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>844</v>
+        <v>780</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="32">
+    <row r="197" spans="1:11" ht="15.6">
       <c r="A197" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="B197" s="4" t="s">
         <v>861</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="C197" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="D197" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="E197" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="D197" s="4" t="s">
-        <v>863</v>
-      </c>
-      <c r="E197" s="4" t="s">
-        <v>863</v>
-      </c>
       <c r="F197" s="4" t="s">
-        <v>248</v>
+        <v>848</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>107</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="K197" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="16">
+    <row r="198" spans="1:11" ht="31.2">
       <c r="A198" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="C198" s="6" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D198" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="E198" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="D198" s="4" t="s">
+      <c r="F198" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J198" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K198" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="31.2">
+      <c r="A199" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="E198" s="4" t="s">
-        <v>866</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>852</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H198" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I198" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="J198" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K198" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" ht="16">
-      <c r="A199" s="4" t="s">
+      <c r="B199" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="C199" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D199" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="C199" s="6" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D199" s="4" t="s">
-        <v>869</v>
-      </c>
       <c r="E199" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>148</v>
@@ -11228,7 +11212,7 @@
         <v>46</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>155</v>
@@ -11237,42 +11221,42 @@
         <v>49</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="16">
+    <row r="200" spans="1:11" ht="31.2">
       <c r="A200" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="B200" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="C200" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="D200" s="4" t="s">
         <v>871</v>
-      </c>
-      <c r="C200" s="6" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D200" s="4" t="s">
-        <v>872</v>
       </c>
       <c r="E200" s="4" t="s">
         <v>872</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>324</v>
+        <v>856</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="32">
+    <row r="201" spans="1:11" ht="31.2">
       <c r="A201" s="4" t="s">
         <v>873</v>
       </c>
@@ -11289,7 +11273,7 @@
         <v>876</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>860</v>
+        <v>877</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>66</v>
@@ -11307,112 +11291,112 @@
         <v>49</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="32">
+    <row r="202" spans="1:11" ht="15.6">
       <c r="A202" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>878</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>1191</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E202" s="4" t="s">
         <v>880</v>
       </c>
       <c r="F202" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I202" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J202" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K202" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" ht="31.2">
+      <c r="A203" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="G202" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H202" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I202" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J202" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K202" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" ht="16">
-      <c r="A203" s="4" t="s">
+      <c r="B203" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="C203" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="D203" s="4" t="s">
         <v>883</v>
-      </c>
-      <c r="C203" s="6" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D203" s="4" t="s">
-        <v>884</v>
       </c>
       <c r="E203" s="4" t="s">
         <v>884</v>
       </c>
       <c r="F203" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I203" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="J203" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K203" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" ht="15.6">
+      <c r="A204" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="F204" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G203" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H203" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I203" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J203" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K203" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" ht="32">
-      <c r="A204" s="4" t="s">
-        <v>885</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>886</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>886</v>
-      </c>
-      <c r="D204" s="4" t="s">
-        <v>887</v>
-      </c>
-      <c r="E204" s="4" t="s">
-        <v>888</v>
-      </c>
-      <c r="F204" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="G204" s="1" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>889</v>
+        <v>47</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="16">
+    <row r="205" spans="1:11" ht="31.2">
       <c r="A205" s="4" t="s">
         <v>890</v>
       </c>
@@ -11420,77 +11404,77 @@
         <v>891</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>892</v>
       </c>
       <c r="E205" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H205" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J205" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="K205" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" ht="31.2">
+      <c r="A206" s="4" t="s">
         <v>893</v>
       </c>
-      <c r="F205" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H205" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I205" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J205" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K205" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" ht="32">
-      <c r="A206" s="4" t="s">
+      <c r="B206" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="C206" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="D206" s="4" t="s">
         <v>895</v>
-      </c>
-      <c r="C206" s="6" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D206" s="4" t="s">
-        <v>896</v>
       </c>
       <c r="E206" s="4" t="s">
         <v>896</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>324</v>
+        <v>244</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="H206" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="32">
+    <row r="207" spans="1:11" ht="31.2">
       <c r="A207" s="4" t="s">
         <v>897</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="C207" s="4" t="s">
-        <v>898</v>
+      <c r="C207" s="6" t="s">
+        <v>1185</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>899</v>
@@ -11499,7 +11483,7 @@
         <v>900</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>66</v>
@@ -11517,24 +11501,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="32">
+    <row r="208" spans="1:11" ht="31.2">
       <c r="A208" s="4" t="s">
         <v>901</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="C208" s="6" t="s">
-        <v>1190</v>
+      <c r="C208" s="4" t="s">
+        <v>902</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>903</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>66</v>
@@ -11543,7 +11527,7 @@
         <v>46</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>67</v>
@@ -11552,24 +11536,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="32">
+    <row r="209" spans="1:11" ht="31.2">
       <c r="A209" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="B209" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="C209" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="D209" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="C209" s="4" t="s">
+      <c r="E209" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="D209" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="E209" s="4" t="s">
-        <v>907</v>
-      </c>
       <c r="F209" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>66</v>
@@ -11578,7 +11562,7 @@
         <v>46</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J209" s="4" t="s">
         <v>67</v>
@@ -11587,42 +11571,42 @@
         <v>49</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="32">
+    <row r="210" spans="1:11" ht="31.2">
       <c r="A210" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="B210" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="C210" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="D210" s="4" t="s">
         <v>909</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="D210" s="4" t="s">
-        <v>910</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>910</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>248</v>
+        <v>44</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="32">
+    <row r="211" spans="1:11" ht="15.6">
       <c r="A211" s="4" t="s">
         <v>911</v>
       </c>
@@ -11642,7 +11626,7 @@
         <v>44</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>46</v>
@@ -11651,91 +11635,91 @@
         <v>47</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="16">
+    <row r="212" spans="1:11" ht="31.2">
       <c r="A212" s="4" t="s">
         <v>915</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="C212" s="4" t="s">
-        <v>916</v>
+      <c r="C212" s="6" t="s">
+        <v>1186</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>917</v>
       </c>
       <c r="E212" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J212" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K212" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" ht="15.6">
+      <c r="A213" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="F212" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H212" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I212" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J212" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K212" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="213" spans="1:11" ht="32">
-      <c r="A213" s="4" t="s">
+      <c r="B213" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="C213" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="D213" s="4" t="s">
         <v>920</v>
-      </c>
-      <c r="C213" s="6" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D213" s="4" t="s">
-        <v>921</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>921</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>248</v>
+        <v>44</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="K213" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="16">
+    <row r="214" spans="1:11" ht="31.2">
       <c r="A214" s="4" t="s">
         <v>922</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C214" s="4" t="s">
-        <v>923</v>
+      <c r="C214" s="6" t="s">
+        <v>1187</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>924</v>
@@ -11744,33 +11728,33 @@
         <v>925</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="H214" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="J214" s="4" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="16">
+    <row r="215" spans="1:11" ht="31.2">
       <c r="A215" s="4" t="s">
         <v>926</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="C215" s="6" t="s">
-        <v>1192</v>
+      <c r="C215" s="4" t="s">
+        <v>927</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>928</v>
@@ -11779,25 +11763,25 @@
         <v>929</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="J215" s="4" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="32">
+    <row r="216" spans="1:11" ht="46.8">
       <c r="A216" s="4" t="s">
         <v>930</v>
       </c>
@@ -11811,74 +11795,74 @@
         <v>932</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>933</v>
+        <v>105</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="J216" s="4" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="48">
+    <row r="217" spans="1:11" ht="15.6">
       <c r="A217" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="B217" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="C217" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D217" s="4" t="s">
         <v>935</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="E217" s="4" t="s">
         <v>935</v>
-      </c>
-      <c r="D217" s="4" t="s">
-        <v>936</v>
-      </c>
-      <c r="E217" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="J217" s="4" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="16">
+    <row r="218" spans="1:11" ht="15.6">
       <c r="A218" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="B218" s="4" t="s">
         <v>937</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="C218" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="D218" s="4" t="s">
         <v>938</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D218" s="4" t="s">
-        <v>939</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>939</v>
@@ -11893,7 +11877,7 @@
         <v>46</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>252</v>
+        <v>47</v>
       </c>
       <c r="J218" s="4" t="s">
         <v>85</v>
@@ -11902,7 +11886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="16">
+    <row r="219" spans="1:11" ht="15.6">
       <c r="A219" s="4" t="s">
         <v>940</v>
       </c>
@@ -11937,15 +11921,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="16">
+    <row r="220" spans="1:11" ht="15.6">
       <c r="A220" s="4" t="s">
         <v>944</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>945</v>
       </c>
-      <c r="C220" s="4" t="s">
-        <v>945</v>
+      <c r="C220" s="6" t="s">
+        <v>1189</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>946</v>
@@ -11954,7 +11938,7 @@
         <v>947</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>44</v>
+        <v>408</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>84</v>
@@ -11972,15 +11956,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="16">
+    <row r="221" spans="1:11" ht="31.2">
       <c r="A221" s="4" t="s">
         <v>948</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>949</v>
       </c>
-      <c r="C221" s="6" t="s">
-        <v>1194</v>
+      <c r="C221" s="4" t="s">
+        <v>949</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>950</v>
@@ -11989,60 +11973,60 @@
         <v>951</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>412</v>
+        <v>320</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="I221" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="J221" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K221" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" ht="15.6">
+      <c r="A222" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H222" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I222" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J221" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K221" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11" ht="32">
-      <c r="A222" s="4" t="s">
-        <v>952</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>954</v>
-      </c>
-      <c r="E222" s="4" t="s">
-        <v>955</v>
-      </c>
-      <c r="F222" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H222" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I222" s="1" t="s">
-        <v>956</v>
-      </c>
       <c r="J222" s="4" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K222" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="16">
+    <row r="223" spans="1:11" ht="31.2">
       <c r="A223" s="4" t="s">
         <v>957</v>
       </c>
@@ -12056,129 +12040,94 @@
         <v>959</v>
       </c>
       <c r="E223" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="J223" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K223" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" ht="15.6">
+      <c r="A224" s="4" t="s">
         <v>960</v>
       </c>
-      <c r="F223" s="4" t="s">
+      <c r="B224" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="F224" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G223" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H223" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I223" s="1" t="s">
+      <c r="G224" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I224" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J223" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K223" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="224" spans="1:11" ht="32">
-      <c r="A224" s="4" t="s">
-        <v>961</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="D224" s="4" t="s">
-        <v>963</v>
-      </c>
-      <c r="E224" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="F224" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H224" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I224" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="J224" s="4" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="16">
+    <row r="225" spans="1:11" ht="15.6">
       <c r="A225" s="4" t="s">
         <v>964</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="C225" s="4" t="s">
-        <v>965</v>
+      <c r="C225" s="6" t="s">
+        <v>1190</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>966</v>
       </c>
       <c r="E225" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="F225" s="4" t="s">
         <v>967</v>
       </c>
-      <c r="F225" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="G225" s="1" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>47</v>
+        <v>248</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="K225" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" ht="16">
-      <c r="A226" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>969</v>
-      </c>
-      <c r="C226" s="6" t="s">
-        <v>1195</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="E226" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="F226" s="4" t="s">
-        <v>971</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H226" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I226" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J226" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K226" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -12191,403 +12140,403 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="21.58203125" customWidth="1"/>
-    <col min="2" max="2" width="43.58203125" customWidth="1"/>
-    <col min="3" max="5" width="60.58203125" customWidth="1"/>
+    <col min="1" max="1" width="21.59765625" customWidth="1"/>
+    <col min="2" max="2" width="43.59765625" customWidth="1"/>
+    <col min="3" max="5" width="60.59765625" customWidth="1"/>
     <col min="6" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28" customHeight="1">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="62.4">
+      <c r="A2" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="64">
-      <c r="A2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="46.8">
+      <c r="A3" s="4" t="s">
         <v>977</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>978</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>980</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="48">
-      <c r="A3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="31.2">
+      <c r="A4" s="4" t="s">
         <v>982</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>983</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="32">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:5" ht="78">
+      <c r="A5" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="31.2">
+      <c r="A6" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="31.2">
+      <c r="A7" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="80">
-      <c r="A5" s="4" t="s">
-        <v>990</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>991</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="32">
-      <c r="A6" s="4" t="s">
-        <v>995</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>996</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="E6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="31.2">
+      <c r="A8" s="4" t="s">
         <v>999</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="32">
-      <c r="A7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>1000</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="31.2">
+      <c r="A9" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.6">
+      <c r="A10" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.6">
+      <c r="A11" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="46.8">
+      <c r="A12" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="31.2">
+      <c r="A13" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="32">
-      <c r="A8" s="4" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="32">
-      <c r="A9" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16">
-      <c r="A10" s="4" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16">
-      <c r="A11" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="48">
-      <c r="A12" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="D13" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="31.2">
+      <c r="A14" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="32">
-      <c r="A13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>1019</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C14" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="31.2">
+      <c r="A15" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="32">
-      <c r="A14" s="4" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="E14" s="1" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="31.2">
+      <c r="A16" s="4" t="s">
         <v>1025</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="32">
-      <c r="A15" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>1026</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C16" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="32">
-      <c r="A16" s="4" t="s">
+    <row r="17" spans="1:5" ht="31.2">
+      <c r="A17" s="4" t="s">
         <v>1029</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>1030</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="32">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:5" ht="31.2">
+      <c r="A18" s="4" t="s">
         <v>1033</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>1034</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="32">
-      <c r="A18" s="4" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>1038</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="32">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="4" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="32">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="4" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.6">
       <c r="A21" s="4" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="32">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="31.2">
+      <c r="A23" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>1048</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C23" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="32">
-      <c r="A23" s="4" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>1053</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -12599,382 +12548,382 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.58203125" customWidth="1"/>
-    <col min="2" max="4" width="60.58203125" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" customWidth="1"/>
+    <col min="2" max="4" width="60.59765625" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28" customHeight="1">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="32">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="32">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="4" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="32">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="4" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="32">
+    <row r="5" spans="1:5" ht="31.2">
       <c r="A5" s="4" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="32">
+    <row r="6" spans="1:5" ht="31.2">
       <c r="A6" s="4" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="32">
+    <row r="7" spans="1:5" ht="31.2">
       <c r="A7" s="4" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="32">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="4" t="s">
         <v>150</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="32">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="4" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="32">
+    <row r="10" spans="1:5" ht="31.2">
       <c r="A10" s="4" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16">
+    <row r="11" spans="1:5" ht="15.6">
       <c r="A11" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16">
+    <row r="12" spans="1:5" ht="15.6">
       <c r="A12" s="4" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="32">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="4" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="32">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="4" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="32">
+    <row r="15" spans="1:5" ht="31.2">
       <c r="A15" s="7" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="E15" s="9">
         <v>46301</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="32">
+    <row r="16" spans="1:5" ht="31.2">
       <c r="A16" s="7" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="E16" s="9">
         <v>46301</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="32">
+    <row r="17" spans="1:5" ht="31.2">
       <c r="A17" s="7" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="E17" s="9">
         <v>46301</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="32">
+    <row r="18" spans="1:5" ht="31.2">
       <c r="A18" s="7" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="E18" s="9">
         <v>46301</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="32">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="7" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="E19" s="9">
         <v>46301</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="32">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="7" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="E20" s="9">
         <v>46301</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="32">
+    <row r="21" spans="1:5" ht="31.2">
       <c r="A21" s="7" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="E21" s="9">
         <v>46301</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="32">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="7" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="E22" s="9">
         <v>46301</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17D3070-7E15-40AC-8EDE-63174D283084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC990BC-13A1-43B0-A581-D0030CB4F53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="검토요약" sheetId="1" r:id="rId1"/>
@@ -3828,7 +3828,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
@@ -3877,9 +3877,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3887,6 +3884,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -4103,14 +4103,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18.59765625" customWidth="1"/>
-    <col min="2" max="2" width="38.59765625" customWidth="1"/>
-    <col min="3" max="3" width="60.59765625" customWidth="1"/>
+    <col min="1" max="1" width="18.58203125" customWidth="1"/>
+    <col min="2" max="2" width="38.58203125" customWidth="1"/>
+    <col min="3" max="3" width="60.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6">
+    <row r="1" spans="1:3" ht="16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6">
+    <row r="2" spans="1:3" ht="16">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6">
+    <row r="3" spans="1:3" ht="16">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6">
+    <row r="4" spans="1:3" ht="16">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6">
+    <row r="5" spans="1:3" ht="16">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6">
+    <row r="8" spans="1:3" ht="16">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6">
+    <row r="9" spans="1:3" ht="16">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6">
+    <row r="10" spans="1:3" ht="16">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="31.2">
+    <row r="11" spans="1:3" ht="32">
       <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
@@ -4240,23 +4240,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K225"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" customWidth="1"/>
-    <col min="2" max="2" width="31.59765625" customWidth="1"/>
-    <col min="3" max="3" width="29.59765625" customWidth="1"/>
-    <col min="4" max="4" width="56.59765625" customWidth="1"/>
-    <col min="5" max="5" width="57.59765625" customWidth="1"/>
-    <col min="6" max="6" width="38.59765625" customWidth="1"/>
-    <col min="7" max="7" width="60.59765625" customWidth="1"/>
-    <col min="8" max="8" width="10.59765625" customWidth="1"/>
-    <col min="9" max="9" width="60.59765625" customWidth="1"/>
-    <col min="10" max="10" width="37.59765625" customWidth="1"/>
-    <col min="11" max="11" width="24.59765625" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="31.58203125" customWidth="1"/>
+    <col min="3" max="3" width="29.58203125" customWidth="1"/>
+    <col min="4" max="4" width="56.58203125" customWidth="1"/>
+    <col min="5" max="5" width="57.58203125" customWidth="1"/>
+    <col min="6" max="6" width="38.58203125" customWidth="1"/>
+    <col min="7" max="7" width="60.58203125" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" customWidth="1"/>
+    <col min="9" max="9" width="60.58203125" customWidth="1"/>
+    <col min="10" max="10" width="37.58203125" customWidth="1"/>
+    <col min="11" max="11" width="24.58203125" customWidth="1"/>
     <col min="12" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.05" customHeight="1">
+    <row r="1" spans="1:11" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
@@ -4291,14 +4291,14 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6">
+    <row r="2" spans="1:11" ht="16">
       <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>1102</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -4326,7 +4326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6">
+    <row r="3" spans="1:11" ht="16">
       <c r="A3" s="4" t="s">
         <v>50</v>
       </c>
@@ -4361,14 +4361,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.6">
+    <row r="4" spans="1:11" ht="16">
       <c r="A4" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>1103</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -4396,14 +4396,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.6">
+    <row r="5" spans="1:11" ht="16">
       <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>1104</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -4431,14 +4431,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="31.2">
+    <row r="6" spans="1:11" ht="32">
       <c r="A6" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="9" t="s">
         <v>1105</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -4466,14 +4466,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="31.2">
+    <row r="7" spans="1:11" ht="32">
       <c r="A7" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="9" t="s">
         <v>1106</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -4501,7 +4501,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="31.2">
+    <row r="8" spans="1:11" ht="32">
       <c r="A8" s="4" t="s">
         <v>72</v>
       </c>
@@ -4536,14 +4536,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="31.2">
+    <row r="9" spans="1:11" ht="32">
       <c r="A9" s="4" t="s">
         <v>76</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="9" t="s">
         <v>1107</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -4571,14 +4571,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.6">
+    <row r="10" spans="1:11" ht="16">
       <c r="A10" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="9" t="s">
         <v>1108</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -4606,14 +4606,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="31.2">
+    <row r="11" spans="1:11" ht="32">
       <c r="A11" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="9" t="s">
         <v>1109</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -4641,14 +4641,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.6">
+    <row r="12" spans="1:11" ht="16">
       <c r="A12" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="9" t="s">
         <v>1110</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -4676,14 +4676,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="31.2">
+    <row r="13" spans="1:11" ht="32">
       <c r="A13" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="9" t="s">
         <v>1111</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -4711,7 +4711,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="46.8">
+    <row r="14" spans="1:11" ht="48">
       <c r="A14" s="4" t="s">
         <v>102</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="31.2">
+    <row r="15" spans="1:11" ht="32">
       <c r="A15" s="4" t="s">
         <v>110</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.6">
+    <row r="16" spans="1:11" ht="16">
       <c r="A16" s="4" t="s">
         <v>114</v>
       </c>
@@ -4816,14 +4816,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.6">
+    <row r="17" spans="1:11" ht="16">
       <c r="A17" s="4" t="s">
         <v>118</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="9" t="s">
         <v>1112</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -4851,14 +4851,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.6">
+    <row r="18" spans="1:11" ht="16">
       <c r="A18" s="4" t="s">
         <v>122</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="9" t="s">
         <v>1113</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -4886,7 +4886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="46.8">
+    <row r="19" spans="1:11" ht="48">
       <c r="A19" s="4" t="s">
         <v>127</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="31.2">
+    <row r="20" spans="1:11" ht="32">
       <c r="A20" s="4" t="s">
         <v>130</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="31.2">
+    <row r="21" spans="1:11" ht="32">
       <c r="A21" s="4" t="s">
         <v>137</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="31.2">
+    <row r="22" spans="1:11" ht="32">
       <c r="A22" s="4" t="s">
         <v>144</v>
       </c>
@@ -5026,14 +5026,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="31.2">
+    <row r="23" spans="1:11" ht="16">
       <c r="A23" s="4" t="s">
         <v>151</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="9" t="s">
         <v>1114</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -5061,14 +5061,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="31.2">
+    <row r="24" spans="1:11" ht="16">
       <c r="A24" s="4" t="s">
         <v>156</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="9" t="s">
         <v>1115</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -5096,7 +5096,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="31.2">
+    <row r="25" spans="1:11" ht="32">
       <c r="A25" s="4" t="s">
         <v>160</v>
       </c>
@@ -5131,14 +5131,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="31.2">
+    <row r="26" spans="1:11" ht="16">
       <c r="A26" s="4" t="s">
         <v>165</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="9" t="s">
         <v>1116</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -5166,7 +5166,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="31.2">
+    <row r="27" spans="1:11" ht="32">
       <c r="A27" s="4" t="s">
         <v>169</v>
       </c>
@@ -5201,14 +5201,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="31.2">
+    <row r="28" spans="1:11" ht="32">
       <c r="A28" s="4" t="s">
         <v>174</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="9" t="s">
         <v>1117</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -5236,14 +5236,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="31.2">
+    <row r="29" spans="1:11" ht="32">
       <c r="A29" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="9" t="s">
         <v>1118</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -5271,14 +5271,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="31.2">
+    <row r="30" spans="1:11" ht="32">
       <c r="A30" s="4" t="s">
         <v>182</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="9" t="s">
         <v>1119</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -5306,14 +5306,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.6">
+    <row r="31" spans="1:11" ht="16">
       <c r="A31" s="4" t="s">
         <v>186</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="9" t="s">
         <v>1120</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -5341,14 +5341,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="31.2">
+    <row r="32" spans="1:11" ht="32">
       <c r="A32" s="4" t="s">
         <v>190</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="9" t="s">
         <v>1121</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -5376,14 +5376,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="31.2">
+    <row r="33" spans="1:11" ht="32">
       <c r="A33" s="4" t="s">
         <v>194</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="9" t="s">
         <v>1122</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -5411,14 +5411,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15.6">
+    <row r="34" spans="1:11" ht="16">
       <c r="A34" s="4" t="s">
         <v>200</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="9" t="s">
         <v>1123</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -5446,14 +5446,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15.6">
+    <row r="35" spans="1:11" ht="16">
       <c r="A35" s="4" t="s">
         <v>204</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="9" t="s">
         <v>1117</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -5481,14 +5481,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15.6">
+    <row r="36" spans="1:11" ht="16">
       <c r="A36" s="4" t="s">
         <v>206</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="9" t="s">
         <v>1124</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -5516,14 +5516,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.6">
+    <row r="37" spans="1:11" ht="16">
       <c r="A37" s="4" t="s">
         <v>210</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="9" t="s">
         <v>1192</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -5551,14 +5551,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.6">
+    <row r="38" spans="1:11" ht="16">
       <c r="A38" s="4" t="s">
         <v>214</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="9" t="s">
         <v>1125</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -5586,7 +5586,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="31.2">
+    <row r="39" spans="1:11" ht="32">
       <c r="A39" s="4" t="s">
         <v>218</v>
       </c>
@@ -5621,14 +5621,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15.6">
+    <row r="40" spans="1:11" ht="16">
       <c r="A40" s="4" t="s">
         <v>222</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="9" t="s">
         <v>1126</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -5656,14 +5656,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="31.2">
+    <row r="41" spans="1:11" ht="32">
       <c r="A41" s="4" t="s">
         <v>226</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="9" t="s">
         <v>1127</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -5691,14 +5691,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15.6">
+    <row r="42" spans="1:11" ht="16">
       <c r="A42" s="4" t="s">
         <v>232</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="9" t="s">
         <v>1128</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -5726,14 +5726,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15.6">
+    <row r="43" spans="1:11" ht="16">
       <c r="A43" s="4" t="s">
         <v>236</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="9" t="s">
         <v>1129</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -5761,14 +5761,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="31.2">
+    <row r="44" spans="1:11" ht="32">
       <c r="A44" s="4" t="s">
         <v>240</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="9" t="s">
         <v>1130</v>
       </c>
       <c r="D44" s="4" t="s">
@@ -5796,14 +5796,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="31.2">
+    <row r="45" spans="1:11" ht="32">
       <c r="A45" s="4" t="s">
         <v>245</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="9" t="s">
         <v>1131</v>
       </c>
       <c r="D45" s="4" t="s">
@@ -5831,14 +5831,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="31.2">
+    <row r="46" spans="1:11" ht="32">
       <c r="A46" s="4" t="s">
         <v>249</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="9" t="s">
         <v>1132</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -5866,14 +5866,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="31.2">
+    <row r="47" spans="1:11" ht="32">
       <c r="A47" s="4" t="s">
         <v>253</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="9" t="s">
         <v>1133</v>
       </c>
       <c r="D47" s="4" t="s">
@@ -5901,7 +5901,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="31.2">
+    <row r="48" spans="1:11" ht="32">
       <c r="A48" s="4" t="s">
         <v>257</v>
       </c>
@@ -5936,14 +5936,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="31.2">
+    <row r="49" spans="1:11" ht="32">
       <c r="A49" s="4" t="s">
         <v>260</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="9" t="s">
         <v>1134</v>
       </c>
       <c r="D49" s="4" t="s">
@@ -5971,7 +5971,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="31.2">
+    <row r="50" spans="1:11" ht="32">
       <c r="A50" s="4" t="s">
         <v>264</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15.6">
+    <row r="51" spans="1:11" ht="16">
       <c r="A51" s="4" t="s">
         <v>268</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="46.8">
+    <row r="52" spans="1:11" ht="48">
       <c r="A52" s="4" t="s">
         <v>272</v>
       </c>
@@ -6076,14 +6076,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.6">
+    <row r="53" spans="1:11" ht="16">
       <c r="A53" s="4" t="s">
         <v>275</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="9" t="s">
         <v>1135</v>
       </c>
       <c r="D53" s="4" t="s">
@@ -6111,7 +6111,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="31.2">
+    <row r="54" spans="1:11" ht="32">
       <c r="A54" s="4" t="s">
         <v>280</v>
       </c>
@@ -6146,14 +6146,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15.6">
+    <row r="55" spans="1:11" ht="16">
       <c r="A55" s="4" t="s">
         <v>284</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="9" t="s">
         <v>1136</v>
       </c>
       <c r="D55" s="4" t="s">
@@ -6181,14 +6181,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15.6">
+    <row r="56" spans="1:11" ht="16">
       <c r="A56" s="4" t="s">
         <v>288</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="9" t="s">
         <v>1137</v>
       </c>
       <c r="D56" s="4" t="s">
@@ -6216,14 +6216,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15.6">
+    <row r="57" spans="1:11" ht="16">
       <c r="A57" s="4" t="s">
         <v>292</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="9" t="s">
         <v>1138</v>
       </c>
       <c r="D57" s="4" t="s">
@@ -6251,14 +6251,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15.6">
+    <row r="58" spans="1:11" ht="16">
       <c r="A58" s="4" t="s">
         <v>296</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="9" t="s">
         <v>1139</v>
       </c>
       <c r="D58" s="4" t="s">
@@ -6286,14 +6286,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="31.2">
+    <row r="59" spans="1:11" ht="32">
       <c r="A59" s="4" t="s">
         <v>299</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="9" t="s">
         <v>1140</v>
       </c>
       <c r="D59" s="4" t="s">
@@ -6321,7 +6321,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="31.2">
+    <row r="60" spans="1:11" ht="32">
       <c r="A60" s="4" t="s">
         <v>303</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="31.2">
+    <row r="61" spans="1:11" ht="32">
       <c r="A61" s="4" t="s">
         <v>310</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="31.2">
+    <row r="62" spans="1:11" ht="32">
       <c r="A62" s="4" t="s">
         <v>316</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="31.2">
+    <row r="63" spans="1:11" ht="32">
       <c r="A63" s="4" t="s">
         <v>322</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="31.2">
+    <row r="64" spans="1:11" ht="32">
       <c r="A64" s="4" t="s">
         <v>327</v>
       </c>
@@ -6496,7 +6496,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="31.2">
+    <row r="65" spans="1:11" ht="16">
       <c r="A65" s="4" t="s">
         <v>333</v>
       </c>
@@ -6531,14 +6531,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="31.2">
+    <row r="66" spans="1:11" ht="16">
       <c r="A66" s="4" t="s">
         <v>338</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="9" t="s">
         <v>1141</v>
       </c>
       <c r="D66" s="4" t="s">
@@ -6566,7 +6566,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="31.2">
+    <row r="67" spans="1:11" ht="32">
       <c r="A67" s="4" t="s">
         <v>342</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="31.2">
+    <row r="68" spans="1:11" ht="32">
       <c r="A68" s="4" t="s">
         <v>348</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="31.2">
+    <row r="69" spans="1:11" ht="16">
       <c r="A69" s="4" t="s">
         <v>353</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="31.2">
+    <row r="70" spans="1:11" ht="32">
       <c r="A70" s="4" t="s">
         <v>359</v>
       </c>
@@ -6706,14 +6706,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="31.2">
+    <row r="71" spans="1:11" ht="32">
       <c r="A71" s="4" t="s">
         <v>364</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="9" t="s">
         <v>1142</v>
       </c>
       <c r="D71" s="4" t="s">
@@ -6741,7 +6741,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="31.2">
+    <row r="72" spans="1:11" ht="32">
       <c r="A72" s="4" t="s">
         <v>367</v>
       </c>
@@ -6776,14 +6776,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="31.2">
+    <row r="73" spans="1:11" ht="32">
       <c r="A73" s="4" t="s">
         <v>371</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="9" t="s">
         <v>1143</v>
       </c>
       <c r="D73" s="4" t="s">
@@ -6811,14 +6811,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="31.2">
+    <row r="74" spans="1:11" ht="32">
       <c r="A74" s="4" t="s">
         <v>375</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="9" t="s">
         <v>1144</v>
       </c>
       <c r="D74" s="4" t="s">
@@ -6846,14 +6846,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="15.6">
+    <row r="75" spans="1:11" ht="16">
       <c r="A75" s="4" t="s">
         <v>379</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="9" t="s">
         <v>1145</v>
       </c>
       <c r="D75" s="4" t="s">
@@ -6881,14 +6881,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15.6">
+    <row r="76" spans="1:11" ht="16">
       <c r="A76" s="4" t="s">
         <v>383</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="9" t="s">
         <v>1146</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -6916,14 +6916,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15.6">
+    <row r="77" spans="1:11" ht="16">
       <c r="A77" s="4" t="s">
         <v>387</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="9" t="s">
         <v>1147</v>
       </c>
       <c r="D77" s="4" t="s">
@@ -6951,14 +6951,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15.6">
+    <row r="78" spans="1:11" ht="16">
       <c r="A78" s="4" t="s">
         <v>391</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="9" t="s">
         <v>1148</v>
       </c>
       <c r="D78" s="4" t="s">
@@ -6986,7 +6986,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="15.6">
+    <row r="79" spans="1:11" ht="16">
       <c r="A79" s="4" t="s">
         <v>395</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="31.2">
+    <row r="80" spans="1:11" ht="32">
       <c r="A80" s="4" t="s">
         <v>399</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="31.2">
+    <row r="81" spans="1:11" ht="32">
       <c r="A81" s="4" t="s">
         <v>404</v>
       </c>
@@ -7091,14 +7091,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="31.2">
+    <row r="82" spans="1:11" ht="32">
       <c r="A82" s="4" t="s">
         <v>410</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="9" t="s">
         <v>1149</v>
       </c>
       <c r="D82" s="4" t="s">
@@ -7126,14 +7126,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="31.2">
+    <row r="83" spans="1:11" ht="32">
       <c r="A83" s="4" t="s">
         <v>415</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="9" t="s">
         <v>1150</v>
       </c>
       <c r="D83" s="4" t="s">
@@ -7161,7 +7161,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="31.2">
+    <row r="84" spans="1:11" ht="32">
       <c r="A84" s="4" t="s">
         <v>419</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="46.8">
+    <row r="85" spans="1:11" ht="48">
       <c r="A85" s="4" t="s">
         <v>424</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="15.6">
+    <row r="86" spans="1:11" ht="16">
       <c r="A86" s="4" t="s">
         <v>428</v>
       </c>
@@ -7266,14 +7266,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="15.6">
+    <row r="87" spans="1:11" ht="16">
       <c r="A87" s="4" t="s">
         <v>432</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="9" t="s">
         <v>1151</v>
       </c>
       <c r="D87" s="4" t="s">
@@ -7301,14 +7301,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="15.6">
+    <row r="88" spans="1:11" ht="16">
       <c r="A88" s="4" t="s">
         <v>436</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="9" t="s">
         <v>1152</v>
       </c>
       <c r="D88" s="4" t="s">
@@ -7336,14 +7336,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15.6">
+    <row r="89" spans="1:11" ht="16">
       <c r="A89" s="4" t="s">
         <v>439</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="9" t="s">
         <v>1153</v>
       </c>
       <c r="D89" s="4" t="s">
@@ -7371,7 +7371,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="15.6">
+    <row r="90" spans="1:11" ht="16">
       <c r="A90" s="4" t="s">
         <v>443</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="31.2">
+    <row r="91" spans="1:11" ht="32">
       <c r="A91" s="4" t="s">
         <v>447</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="31.2">
+    <row r="92" spans="1:11" ht="32">
       <c r="A92" s="4" t="s">
         <v>451</v>
       </c>
@@ -7476,14 +7476,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="31.2">
+    <row r="93" spans="1:11" ht="32">
       <c r="A93" s="4" t="s">
         <v>455</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="9" t="s">
         <v>1154</v>
       </c>
       <c r="D93" s="4" t="s">
@@ -7511,14 +7511,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="31.2">
+    <row r="94" spans="1:11" ht="32">
       <c r="A94" s="4" t="s">
         <v>459</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="9" t="s">
         <v>1155</v>
       </c>
       <c r="D94" s="4" t="s">
@@ -7546,14 +7546,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="31.2">
+    <row r="95" spans="1:11" ht="32">
       <c r="A95" s="4" t="s">
         <v>463</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="9" t="s">
         <v>1156</v>
       </c>
       <c r="D95" s="4" t="s">
@@ -7581,7 +7581,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="15.6">
+    <row r="96" spans="1:11" ht="16">
       <c r="A96" s="4" t="s">
         <v>467</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15.6">
+    <row r="97" spans="1:11" ht="16">
       <c r="A97" s="4" t="s">
         <v>471</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15.6">
+    <row r="98" spans="1:11" ht="16">
       <c r="A98" s="4" t="s">
         <v>475</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="31.2">
+    <row r="99" spans="1:11" ht="32">
       <c r="A99" s="4" t="s">
         <v>479</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15.6">
+    <row r="100" spans="1:11" ht="16">
       <c r="A100" s="4" t="s">
         <v>484</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="46.8">
+    <row r="101" spans="1:11" ht="48">
       <c r="A101" s="4" t="s">
         <v>488</v>
       </c>
@@ -7791,14 +7791,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="15.6">
+    <row r="102" spans="1:11" ht="16">
       <c r="A102" s="4" t="s">
         <v>491</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="9" t="s">
         <v>1157</v>
       </c>
       <c r="D102" s="4" t="s">
@@ -7826,7 +7826,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="15.6">
+    <row r="103" spans="1:11" ht="16">
       <c r="A103" s="4" t="s">
         <v>494</v>
       </c>
@@ -7861,14 +7861,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="15.6">
+    <row r="104" spans="1:11" ht="16">
       <c r="A104" s="4" t="s">
         <v>497</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="9" t="s">
         <v>1158</v>
       </c>
       <c r="D104" s="4" t="s">
@@ -7896,14 +7896,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="15.6">
+    <row r="105" spans="1:11" ht="16">
       <c r="A105" s="4" t="s">
         <v>501</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="9" t="s">
         <v>1159</v>
       </c>
       <c r="D105" s="4" t="s">
@@ -7931,7 +7931,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="15.6">
+    <row r="106" spans="1:11" ht="16">
       <c r="A106" s="4" t="s">
         <v>505</v>
       </c>
@@ -7966,14 +7966,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="15.6">
+    <row r="107" spans="1:11" ht="16">
       <c r="A107" s="4" t="s">
         <v>509</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="9" t="s">
         <v>1160</v>
       </c>
       <c r="D107" s="4" t="s">
@@ -8001,7 +8001,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="31.2">
+    <row r="108" spans="1:11" ht="32">
       <c r="A108" s="4" t="s">
         <v>513</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="31.2">
+    <row r="109" spans="1:11" ht="32">
       <c r="A109" s="4" t="s">
         <v>518</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="31.2">
+    <row r="110" spans="1:11" ht="16">
       <c r="A110" s="4" t="s">
         <v>526</v>
       </c>
@@ -8106,7 +8106,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="31.2">
+    <row r="111" spans="1:11" ht="32">
       <c r="A111" s="4" t="s">
         <v>530</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="31.2">
+    <row r="112" spans="1:11" ht="32">
       <c r="A112" s="4" t="s">
         <v>534</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="31.2">
+    <row r="113" spans="1:11" ht="32">
       <c r="A113" s="4" t="s">
         <v>539</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="31.2">
+    <row r="114" spans="1:11" ht="32">
       <c r="A114" s="4" t="s">
         <v>544</v>
       </c>
@@ -8246,14 +8246,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="31.2">
+    <row r="115" spans="1:11" ht="32">
       <c r="A115" s="4" t="s">
         <v>548</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C115" s="9" t="s">
         <v>1161</v>
       </c>
       <c r="D115" s="4" t="s">
@@ -8281,7 +8281,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="31.2">
+    <row r="116" spans="1:11" ht="16">
       <c r="A116" s="4" t="s">
         <v>551</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="31.2">
+    <row r="117" spans="1:11" ht="32">
       <c r="A117" s="4" t="s">
         <v>554</v>
       </c>
@@ -8351,14 +8351,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="31.2">
+    <row r="118" spans="1:11" ht="16">
       <c r="A118" s="4" t="s">
         <v>559</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="9" t="s">
         <v>1162</v>
       </c>
       <c r="D118" s="4" t="s">
@@ -8386,14 +8386,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="31.2">
+    <row r="119" spans="1:11" ht="32">
       <c r="A119" s="4" t="s">
         <v>563</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="9" t="s">
         <v>1163</v>
       </c>
       <c r="D119" s="4" t="s">
@@ -8421,7 +8421,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="31.2">
+    <row r="120" spans="1:11" ht="32">
       <c r="A120" s="4" t="s">
         <v>567</v>
       </c>
@@ -8456,14 +8456,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="31.2">
+    <row r="121" spans="1:11" ht="32">
       <c r="A121" s="4" t="s">
         <v>571</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C121" s="6" t="s">
+      <c r="C121" s="9" t="s">
         <v>1164</v>
       </c>
       <c r="D121" s="4" t="s">
@@ -8491,14 +8491,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="31.2">
+    <row r="122" spans="1:11" ht="32">
       <c r="A122" s="4" t="s">
         <v>575</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C122" s="9" t="s">
         <v>1165</v>
       </c>
       <c r="D122" s="4" t="s">
@@ -8526,7 +8526,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="31.2">
+    <row r="123" spans="1:11" ht="32">
       <c r="A123" s="4" t="s">
         <v>578</v>
       </c>
@@ -8561,14 +8561,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="31.2">
+    <row r="124" spans="1:11" ht="32">
       <c r="A124" s="4" t="s">
         <v>583</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="9" t="s">
         <v>1166</v>
       </c>
       <c r="D124" s="4" t="s">
@@ -8596,7 +8596,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="15.6">
+    <row r="125" spans="1:11" ht="16">
       <c r="A125" s="4" t="s">
         <v>587</v>
       </c>
@@ -8631,14 +8631,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="15.6">
+    <row r="126" spans="1:11" ht="16">
       <c r="A126" s="4" t="s">
         <v>591</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" s="9" t="s">
         <v>1167</v>
       </c>
       <c r="D126" s="4" t="s">
@@ -8666,7 +8666,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="31.2">
+    <row r="127" spans="1:11" ht="32">
       <c r="A127" s="4" t="s">
         <v>594</v>
       </c>
@@ -8701,7 +8701,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="31.2">
+    <row r="128" spans="1:11" ht="32">
       <c r="A128" s="4" t="s">
         <v>599</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="31.2">
+    <row r="129" spans="1:11" ht="32">
       <c r="A129" s="4" t="s">
         <v>604</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="31.2">
+    <row r="130" spans="1:11" ht="32">
       <c r="A130" s="4" t="s">
         <v>609</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="15.6">
+    <row r="131" spans="1:11" ht="16">
       <c r="A131" s="4" t="s">
         <v>614</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="15.6">
+    <row r="132" spans="1:11" ht="16">
       <c r="A132" s="4" t="s">
         <v>617</v>
       </c>
@@ -8876,7 +8876,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="15.6">
+    <row r="133" spans="1:11" ht="16">
       <c r="A133" s="4" t="s">
         <v>620</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="15.6">
+    <row r="134" spans="1:11" ht="16">
       <c r="A134" s="4" t="s">
         <v>623</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="15.6">
+    <row r="135" spans="1:11" ht="16">
       <c r="A135" s="4" t="s">
         <v>626</v>
       </c>
@@ -8981,14 +8981,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15.6">
+    <row r="136" spans="1:11" ht="16">
       <c r="A136" s="4" t="s">
         <v>630</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C136" s="9" t="s">
         <v>1168</v>
       </c>
       <c r="D136" s="4" t="s">
@@ -9016,7 +9016,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="31.2">
+    <row r="137" spans="1:11" ht="32">
       <c r="A137" s="4" t="s">
         <v>634</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="15.6">
+    <row r="138" spans="1:11" ht="16">
       <c r="A138" s="4" t="s">
         <v>637</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="31.2">
+    <row r="139" spans="1:11" ht="32">
       <c r="A139" s="4" t="s">
         <v>640</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="31.2">
+    <row r="140" spans="1:11" ht="32">
       <c r="A140" s="4" t="s">
         <v>644</v>
       </c>
@@ -9156,14 +9156,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="15.6">
+    <row r="141" spans="1:11" ht="16">
       <c r="A141" s="4" t="s">
         <v>648</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C141" s="9" t="s">
         <v>1169</v>
       </c>
       <c r="D141" s="4" t="s">
@@ -9191,7 +9191,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="31.2">
+    <row r="142" spans="1:11" ht="32">
       <c r="A142" s="4" t="s">
         <v>651</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="15.6">
+    <row r="143" spans="1:11" ht="16">
       <c r="A143" s="4" t="s">
         <v>656</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="15.6">
+    <row r="144" spans="1:11" ht="16">
       <c r="A144" s="4" t="s">
         <v>659</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="15.6">
+    <row r="145" spans="1:11" ht="16">
       <c r="A145" s="4" t="s">
         <v>662</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="15.6">
+    <row r="146" spans="1:11" ht="16">
       <c r="A146" s="4" t="s">
         <v>667</v>
       </c>
@@ -9366,14 +9366,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="31.2">
+    <row r="147" spans="1:11" ht="32">
       <c r="A147" s="4" t="s">
         <v>671</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="C147" s="6" t="s">
+      <c r="C147" s="9" t="s">
         <v>1170</v>
       </c>
       <c r="D147" s="4" t="s">
@@ -9401,14 +9401,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="15.6">
+    <row r="148" spans="1:11" ht="16">
       <c r="A148" s="4" t="s">
         <v>674</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C148" s="9" t="s">
         <v>1171</v>
       </c>
       <c r="D148" s="4" t="s">
@@ -9436,14 +9436,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="15.6">
+    <row r="149" spans="1:11" ht="16">
       <c r="A149" s="4" t="s">
         <v>678</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="C149" s="6" t="s">
+      <c r="C149" s="9" t="s">
         <v>1172</v>
       </c>
       <c r="D149" s="4" t="s">
@@ -9471,7 +9471,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="15.6">
+    <row r="150" spans="1:11" ht="16">
       <c r="A150" s="4" t="s">
         <v>681</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="15.6">
+    <row r="151" spans="1:11" ht="16">
       <c r="A151" s="4" t="s">
         <v>685</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="15.6">
+    <row r="152" spans="1:11" ht="16">
       <c r="A152" s="4" t="s">
         <v>688</v>
       </c>
@@ -9576,14 +9576,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="15.6">
+    <row r="153" spans="1:11" ht="16">
       <c r="A153" s="4" t="s">
         <v>692</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C153" s="9" t="s">
         <v>1173</v>
       </c>
       <c r="D153" s="4" t="s">
@@ -9611,7 +9611,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="31.2">
+    <row r="154" spans="1:11" ht="32">
       <c r="A154" s="4" t="s">
         <v>696</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="31.2">
+    <row r="155" spans="1:11" ht="32">
       <c r="A155" s="4" t="s">
         <v>700</v>
       </c>
@@ -9681,14 +9681,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="31.2">
+    <row r="156" spans="1:11" ht="16">
       <c r="A156" s="4" t="s">
         <v>704</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="C156" s="6" t="s">
+      <c r="C156" s="9" t="s">
         <v>1174</v>
       </c>
       <c r="D156" s="4" t="s">
@@ -9716,14 +9716,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="31.2">
+    <row r="157" spans="1:11" ht="16">
       <c r="A157" s="4" t="s">
         <v>707</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C157" s="9" t="s">
         <v>1175</v>
       </c>
       <c r="D157" s="4" t="s">
@@ -9751,7 +9751,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="31.2">
+    <row r="158" spans="1:11" ht="32">
       <c r="A158" s="4" t="s">
         <v>711</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="31.2">
+    <row r="159" spans="1:11" ht="16">
       <c r="A159" s="4" t="s">
         <v>716</v>
       </c>
@@ -9821,7 +9821,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="31.2">
+    <row r="160" spans="1:11" ht="16">
       <c r="A160" s="4" t="s">
         <v>722</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="31.2">
+    <row r="161" spans="1:11" ht="32">
       <c r="A161" s="4" t="s">
         <v>726</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="31.2">
+    <row r="162" spans="1:11" ht="32">
       <c r="A162" s="4" t="s">
         <v>729</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="31.2">
+    <row r="163" spans="1:11" ht="16">
       <c r="A163" s="4" t="s">
         <v>734</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="31.2">
+    <row r="164" spans="1:11" ht="32">
       <c r="A164" s="4" t="s">
         <v>737</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="31.2">
+    <row r="165" spans="1:11" ht="32">
       <c r="A165" s="4" t="s">
         <v>741</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="31.2">
+    <row r="166" spans="1:11" ht="32">
       <c r="A166" s="4" t="s">
         <v>744</v>
       </c>
@@ -10066,7 +10066,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="31.2">
+    <row r="167" spans="1:11" ht="32">
       <c r="A167" s="4" t="s">
         <v>747</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="31.2">
+    <row r="168" spans="1:11" ht="32">
       <c r="A168" s="4" t="s">
         <v>750</v>
       </c>
@@ -10136,7 +10136,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="31.2">
+    <row r="169" spans="1:11" ht="32">
       <c r="A169" s="4" t="s">
         <v>754</v>
       </c>
@@ -10171,7 +10171,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="31.2">
+    <row r="170" spans="1:11" ht="32">
       <c r="A170" s="4" t="s">
         <v>758</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="15.6">
+    <row r="171" spans="1:11" ht="16">
       <c r="A171" s="4" t="s">
         <v>761</v>
       </c>
@@ -10241,14 +10241,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="15.6">
+    <row r="172" spans="1:11" ht="16">
       <c r="A172" s="4" t="s">
         <v>765</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="C172" s="6" t="s">
+      <c r="C172" s="9" t="s">
         <v>1176</v>
       </c>
       <c r="D172" s="4" t="s">
@@ -10276,14 +10276,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="15.6">
+    <row r="173" spans="1:11" ht="16">
       <c r="A173" s="4" t="s">
         <v>769</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="C173" s="6" t="s">
+      <c r="C173" s="9" t="s">
         <v>1177</v>
       </c>
       <c r="D173" s="4" t="s">
@@ -10311,7 +10311,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="15.6">
+    <row r="174" spans="1:11" ht="16">
       <c r="A174" s="4" t="s">
         <v>773</v>
       </c>
@@ -10346,7 +10346,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="31.2">
+    <row r="175" spans="1:11" ht="32">
       <c r="A175" s="4" t="s">
         <v>777</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="31.2">
+    <row r="176" spans="1:11" ht="32">
       <c r="A176" s="4" t="s">
         <v>781</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="31.2">
+    <row r="177" spans="1:11" ht="32">
       <c r="A177" s="4" t="s">
         <v>786</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="15.6">
+    <row r="178" spans="1:11" ht="16">
       <c r="A178" s="4" t="s">
         <v>789</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="31.2">
+    <row r="179" spans="1:11" ht="32">
       <c r="A179" s="4" t="s">
         <v>792</v>
       </c>
@@ -10521,14 +10521,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15.6">
+    <row r="180" spans="1:11" ht="16">
       <c r="A180" s="4" t="s">
         <v>797</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>798</v>
       </c>
-      <c r="C180" s="6" t="s">
+      <c r="C180" s="9" t="s">
         <v>1178</v>
       </c>
       <c r="D180" s="4" t="s">
@@ -10556,14 +10556,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="15.6">
+    <row r="181" spans="1:11" ht="16">
       <c r="A181" s="4" t="s">
         <v>801</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>802</v>
       </c>
-      <c r="C181" s="6" t="s">
+      <c r="C181" s="9" t="s">
         <v>1179</v>
       </c>
       <c r="D181" s="4" t="s">
@@ -10591,14 +10591,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="31.2">
+    <row r="182" spans="1:11" ht="32">
       <c r="A182" s="4" t="s">
         <v>805</v>
       </c>
       <c r="B182" s="4" t="s">
         <v>806</v>
       </c>
-      <c r="C182" s="6" t="s">
+      <c r="C182" s="9" t="s">
         <v>1180</v>
       </c>
       <c r="D182" s="4" t="s">
@@ -10626,7 +10626,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="31.2">
+    <row r="183" spans="1:11" ht="32">
       <c r="A183" s="4" t="s">
         <v>809</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15.6">
+    <row r="184" spans="1:11" ht="16">
       <c r="A184" s="4" t="s">
         <v>813</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="31.2">
+    <row r="185" spans="1:11" ht="32">
       <c r="A185" s="4" t="s">
         <v>816</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="31.2">
+    <row r="186" spans="1:11" ht="32">
       <c r="A186" s="4" t="s">
         <v>819</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="31.2">
+    <row r="187" spans="1:11" ht="32">
       <c r="A187" s="4" t="s">
         <v>823</v>
       </c>
@@ -10801,7 +10801,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="31.2">
+    <row r="188" spans="1:11" ht="32">
       <c r="A188" s="4" t="s">
         <v>827</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="31.2">
+    <row r="189" spans="1:11" ht="32">
       <c r="A189" s="4" t="s">
         <v>831</v>
       </c>
@@ -10871,7 +10871,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="15.6">
+    <row r="190" spans="1:11" ht="16">
       <c r="A190" s="4" t="s">
         <v>834</v>
       </c>
@@ -10906,7 +10906,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="31.2">
+    <row r="191" spans="1:11" ht="32">
       <c r="A191" s="4" t="s">
         <v>837</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="31.2">
+    <row r="192" spans="1:11" ht="32">
       <c r="A192" s="4" t="s">
         <v>841</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="31.2">
+    <row r="193" spans="1:11" ht="32">
       <c r="A193" s="4" t="s">
         <v>844</v>
       </c>
@@ -11011,7 +11011,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="31.2">
+    <row r="194" spans="1:11" ht="32">
       <c r="A194" s="4" t="s">
         <v>849</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="31.2">
+    <row r="195" spans="1:11" ht="32">
       <c r="A195" s="4" t="s">
         <v>853</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="31.2">
+    <row r="196" spans="1:11" ht="32">
       <c r="A196" s="4" t="s">
         <v>857</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="15.6">
+    <row r="197" spans="1:11" ht="16">
       <c r="A197" s="4" t="s">
         <v>860</v>
       </c>
@@ -11151,14 +11151,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="31.2">
+    <row r="198" spans="1:11" ht="16">
       <c r="A198" s="4" t="s">
         <v>863</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="C198" s="6" t="s">
+      <c r="C198" s="9" t="s">
         <v>1181</v>
       </c>
       <c r="D198" s="4" t="s">
@@ -11186,14 +11186,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="31.2">
+    <row r="199" spans="1:11" ht="16">
       <c r="A199" s="4" t="s">
         <v>866</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="C199" s="6" t="s">
+      <c r="C199" s="9" t="s">
         <v>1182</v>
       </c>
       <c r="D199" s="4" t="s">
@@ -11221,7 +11221,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="31.2">
+    <row r="200" spans="1:11" ht="32">
       <c r="A200" s="4" t="s">
         <v>869</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="31.2">
+    <row r="201" spans="1:11" ht="32">
       <c r="A201" s="4" t="s">
         <v>873</v>
       </c>
@@ -11291,14 +11291,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="15.6">
+    <row r="202" spans="1:11" ht="16">
       <c r="A202" s="4" t="s">
         <v>878</v>
       </c>
       <c r="B202" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="C202" s="6" t="s">
+      <c r="C202" s="9" t="s">
         <v>1191</v>
       </c>
       <c r="D202" s="4" t="s">
@@ -11326,7 +11326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="31.2">
+    <row r="203" spans="1:11" ht="32">
       <c r="A203" s="4" t="s">
         <v>881</v>
       </c>
@@ -11361,14 +11361,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="15.6">
+    <row r="204" spans="1:11" ht="16">
       <c r="A204" s="4" t="s">
         <v>886</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="C204" s="6" t="s">
+      <c r="C204" s="9" t="s">
         <v>1183</v>
       </c>
       <c r="D204" s="4" t="s">
@@ -11396,14 +11396,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="31.2">
+    <row r="205" spans="1:11" ht="32">
       <c r="A205" s="4" t="s">
         <v>890</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="C205" s="6" t="s">
+      <c r="C205" s="9" t="s">
         <v>1184</v>
       </c>
       <c r="D205" s="4" t="s">
@@ -11431,7 +11431,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="31.2">
+    <row r="206" spans="1:11" ht="32">
       <c r="A206" s="4" t="s">
         <v>893</v>
       </c>
@@ -11466,14 +11466,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="31.2">
+    <row r="207" spans="1:11" ht="32">
       <c r="A207" s="4" t="s">
         <v>897</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="C207" s="6" t="s">
+      <c r="C207" s="9" t="s">
         <v>1185</v>
       </c>
       <c r="D207" s="4" t="s">
@@ -11501,7 +11501,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="31.2">
+    <row r="208" spans="1:11" ht="32">
       <c r="A208" s="4" t="s">
         <v>901</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="31.2">
+    <row r="209" spans="1:11" ht="32">
       <c r="A209" s="4" t="s">
         <v>904</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="31.2">
+    <row r="210" spans="1:11" ht="32">
       <c r="A210" s="4" t="s">
         <v>907</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="15.6">
+    <row r="211" spans="1:11" ht="16">
       <c r="A211" s="4" t="s">
         <v>911</v>
       </c>
@@ -11641,14 +11641,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="31.2">
+    <row r="212" spans="1:11" ht="32">
       <c r="A212" s="4" t="s">
         <v>915</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C212" s="9" t="s">
         <v>1186</v>
       </c>
       <c r="D212" s="4" t="s">
@@ -11676,7 +11676,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="15.6">
+    <row r="213" spans="1:11" ht="16">
       <c r="A213" s="4" t="s">
         <v>918</v>
       </c>
@@ -11711,14 +11711,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="31.2">
+    <row r="214" spans="1:11" ht="16">
       <c r="A214" s="4" t="s">
         <v>922</v>
       </c>
       <c r="B214" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C214" s="9" t="s">
         <v>1187</v>
       </c>
       <c r="D214" s="4" t="s">
@@ -11746,7 +11746,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="31.2">
+    <row r="215" spans="1:11" ht="32">
       <c r="A215" s="4" t="s">
         <v>926</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="46.8">
+    <row r="216" spans="1:11" ht="48">
       <c r="A216" s="4" t="s">
         <v>930</v>
       </c>
@@ -11816,14 +11816,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="15.6">
+    <row r="217" spans="1:11" ht="16">
       <c r="A217" s="4" t="s">
         <v>933</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C217" s="9" t="s">
         <v>1188</v>
       </c>
       <c r="D217" s="4" t="s">
@@ -11851,7 +11851,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="15.6">
+    <row r="218" spans="1:11" ht="16">
       <c r="A218" s="4" t="s">
         <v>936</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="15.6">
+    <row r="219" spans="1:11" ht="16">
       <c r="A219" s="4" t="s">
         <v>940</v>
       </c>
@@ -11921,14 +11921,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="15.6">
+    <row r="220" spans="1:11" ht="16">
       <c r="A220" s="4" t="s">
         <v>944</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>945</v>
       </c>
-      <c r="C220" s="6" t="s">
+      <c r="C220" s="9" t="s">
         <v>1189</v>
       </c>
       <c r="D220" s="4" t="s">
@@ -11956,7 +11956,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="31.2">
+    <row r="221" spans="1:11" ht="32">
       <c r="A221" s="4" t="s">
         <v>948</v>
       </c>
@@ -11991,7 +11991,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="15.6">
+    <row r="222" spans="1:11" ht="16">
       <c r="A222" s="4" t="s">
         <v>953</v>
       </c>
@@ -12026,7 +12026,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="31.2">
+    <row r="223" spans="1:11" ht="32">
       <c r="A223" s="4" t="s">
         <v>957</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="15.6">
+    <row r="224" spans="1:11" ht="16">
       <c r="A224" s="4" t="s">
         <v>960</v>
       </c>
@@ -12096,14 +12096,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="15.6">
+    <row r="225" spans="1:11" ht="16">
       <c r="A225" s="4" t="s">
         <v>964</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="C225" s="6" t="s">
+      <c r="C225" s="9" t="s">
         <v>1190</v>
       </c>
       <c r="D225" s="4" t="s">
@@ -12140,15 +12140,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="21.59765625" customWidth="1"/>
-    <col min="2" max="2" width="43.59765625" customWidth="1"/>
-    <col min="3" max="5" width="60.59765625" customWidth="1"/>
+    <col min="1" max="1" width="21.58203125" customWidth="1"/>
+    <col min="2" max="2" width="43.58203125" customWidth="1"/>
+    <col min="3" max="5" width="60.58203125" customWidth="1"/>
     <col min="6" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+    <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>968</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="62.4">
+    <row r="2" spans="1:5" ht="64">
       <c r="A2" s="4" t="s">
         <v>972</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="46.8">
+    <row r="3" spans="1:5" ht="48">
       <c r="A3" s="4" t="s">
         <v>977</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="32">
       <c r="A4" s="4" t="s">
         <v>982</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="78">
+    <row r="5" spans="1:5" ht="80">
       <c r="A5" s="4" t="s">
         <v>986</v>
       </c>
@@ -12233,7 +12233,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="31.2">
+    <row r="6" spans="1:5" ht="32">
       <c r="A6" s="4" t="s">
         <v>991</v>
       </c>
@@ -12250,7 +12250,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="31.2">
+    <row r="7" spans="1:5" ht="32">
       <c r="A7" s="4" t="s">
         <v>996</v>
       </c>
@@ -12267,7 +12267,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="32">
       <c r="A8" s="4" t="s">
         <v>999</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="32">
       <c r="A9" s="4" t="s">
         <v>320</v>
       </c>
@@ -12301,7 +12301,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" s="4" t="s">
         <v>1006</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.6">
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" s="4" t="s">
         <v>1009</v>
       </c>
@@ -12335,7 +12335,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="46.8">
+    <row r="12" spans="1:5" ht="48">
       <c r="A12" s="4" t="s">
         <v>1012</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="32">
       <c r="A13" s="4" t="s">
         <v>1015</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="32">
       <c r="A14" s="4" t="s">
         <v>1018</v>
       </c>
@@ -12386,7 +12386,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="31.2">
+    <row r="15" spans="1:5" ht="32">
       <c r="A15" s="4" t="s">
         <v>1022</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="31.2">
+    <row r="16" spans="1:5" ht="32">
       <c r="A16" s="4" t="s">
         <v>1025</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="31.2">
+    <row r="17" spans="1:5" ht="32">
       <c r="A17" s="4" t="s">
         <v>1029</v>
       </c>
@@ -12437,7 +12437,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="31.2">
+    <row r="18" spans="1:5" ht="32">
       <c r="A18" s="4" t="s">
         <v>1033</v>
       </c>
@@ -12454,7 +12454,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="32">
       <c r="A19" s="4" t="s">
         <v>1036</v>
       </c>
@@ -12471,7 +12471,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="32">
       <c r="A20" s="4" t="s">
         <v>1039</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6">
+    <row r="21" spans="1:5" ht="16">
       <c r="A21" s="4" t="s">
         <v>1042</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="32">
       <c r="A22" s="4" t="s">
         <v>1044</v>
       </c>
@@ -12522,7 +12522,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="31.2">
+    <row r="23" spans="1:5" ht="32">
       <c r="A23" s="4" t="s">
         <v>1047</v>
       </c>
@@ -12548,14 +12548,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="4" width="60.59765625" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" customWidth="1"/>
+    <col min="1" max="1" width="17.58203125" customWidth="1"/>
+    <col min="2" max="4" width="60.58203125" customWidth="1"/>
+    <col min="5" max="5" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+    <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -12572,7 +12572,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="32">
       <c r="A2" s="4" t="s">
         <v>48</v>
       </c>
@@ -12589,7 +12589,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="32">
       <c r="A3" s="4" t="s">
         <v>1057</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="32">
       <c r="A4" s="4" t="s">
         <v>1061</v>
       </c>
@@ -12623,7 +12623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="31.2">
+    <row r="5" spans="1:5" ht="32">
       <c r="A5" s="4" t="s">
         <v>1065</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="31.2">
+    <row r="6" spans="1:5" ht="32">
       <c r="A6" s="4" t="s">
         <v>1069</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="31.2">
+    <row r="7" spans="1:5" ht="32">
       <c r="A7" s="4" t="s">
         <v>1073</v>
       </c>
@@ -12674,7 +12674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="32">
       <c r="A8" s="4" t="s">
         <v>150</v>
       </c>
@@ -12691,7 +12691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="32">
       <c r="A9" s="4" t="s">
         <v>995</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="31.2">
+    <row r="10" spans="1:5" ht="32">
       <c r="A10" s="4" t="s">
         <v>1083</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.6">
+    <row r="11" spans="1:5" ht="16">
       <c r="A11" s="4" t="s">
         <v>309</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.6">
+    <row r="12" spans="1:5" ht="16">
       <c r="A12" s="4" t="s">
         <v>1090</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="32">
       <c r="A13" s="4" t="s">
         <v>1094</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="32">
       <c r="A14" s="4" t="s">
         <v>1098</v>
       </c>
@@ -12793,139 +12793,139 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="31.2">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:5" ht="32">
+      <c r="A15" s="6" t="s">
         <v>1193</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>1195</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>1196</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>46301</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="31.2">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:5" ht="32">
+      <c r="A16" s="6" t="s">
         <v>1197</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>1198</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>1199</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>1200</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>46301</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="31.2">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:5" ht="32">
+      <c r="A17" s="6" t="s">
         <v>1201</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>1202</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>1203</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>1204</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>46301</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="31.2">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:5" ht="32">
+      <c r="A18" s="6" t="s">
         <v>1205</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>1207</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>1208</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>46301</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" ht="32">
+      <c r="A19" s="6" t="s">
         <v>1209</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>1210</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>1211</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <v>46301</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" ht="32">
+      <c r="A20" s="6" t="s">
         <v>1213</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>1214</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>1215</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>1216</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <v>46301</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="31.2">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:5" ht="32">
+      <c r="A21" s="6" t="s">
         <v>1217</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>1218</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>1219</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>1220</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <v>46301</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:5" ht="32">
+      <c r="A22" s="6" t="s">
         <v>1221</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>1222</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>1219</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <v>46301</v>
       </c>
     </row>

--- a/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1105603E-572B-4195-B771-8229E7D68AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ABE9C9-5CA9-4AD7-894F-94E342010935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5218" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5219" uniqueCount="2094">
   <si>
     <t>항목</t>
   </si>
@@ -6417,13 +6417,85 @@
   <si>
     <t>KDA-2023; MOHW-DIETGUIDE</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>식이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>의학</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대조</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · v1.1.0 · 2026-10-13</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -6475,6 +6547,19 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6502,7 +6587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6540,6 +6625,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -6753,7 +6839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18.58203125" customWidth="1"/>
@@ -6761,7 +6847,7 @@
     <col min="3" max="3" width="60.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16">
+    <row r="1" spans="1:5" ht="16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6771,8 +6857,11 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="16">
+      <c r="E1" s="13" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -6783,7 +6872,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -6794,7 +6883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="32">
+    <row r="4" spans="1:5" ht="32">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -6805,7 +6894,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -6816,7 +6905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -6827,7 +6916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16">
+    <row r="7" spans="1:5" ht="16">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -6838,7 +6927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16">
+    <row r="8" spans="1:5" ht="16">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -6849,7 +6938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16">
+    <row r="9" spans="1:5" ht="16">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -6860,7 +6949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16">
+    <row r="10" spans="1:5" ht="16">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -6871,7 +6960,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32">
+    <row r="11" spans="1:5" ht="32">
       <c r="A11" s="4" t="s">
         <v>25</v>
       </c>

--- a/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_의학근거대조_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9185CB84-4E26-4E27-BF2C-A56CD63A2C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D55366-7C0C-4325-A965-27094CF58CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6488,7 +6488,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -6536,13 +6536,6 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6570,7 +6563,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -6600,9 +6593,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -14855,7 +14845,7 @@
       <c r="B226" s="4" t="s">
         <v>1224</v>
       </c>
-      <c r="C226" s="11" t="s">
+      <c r="C226" s="4" t="s">
         <v>1225</v>
       </c>
       <c r="D226" s="4" t="s">
@@ -14890,7 +14880,7 @@
       <c r="B227" s="4" t="s">
         <v>1228</v>
       </c>
-      <c r="C227" s="11" t="s">
+      <c r="C227" s="4" t="s">
         <v>1229</v>
       </c>
       <c r="D227" s="4" t="s">
@@ -14925,7 +14915,7 @@
       <c r="B228" s="4" t="s">
         <v>1232</v>
       </c>
-      <c r="C228" s="11" t="s">
+      <c r="C228" s="4" t="s">
         <v>1233</v>
       </c>
       <c r="D228" s="4" t="s">
@@ -14960,7 +14950,7 @@
       <c r="B229" s="4" t="s">
         <v>1236</v>
       </c>
-      <c r="C229" s="11" t="s">
+      <c r="C229" s="4" t="s">
         <v>1237</v>
       </c>
       <c r="D229" s="4" t="s">
@@ -14995,7 +14985,7 @@
       <c r="B230" s="4" t="s">
         <v>1240</v>
       </c>
-      <c r="C230" s="11" t="s">
+      <c r="C230" s="4" t="s">
         <v>1241</v>
       </c>
       <c r="D230" s="4" t="s">
@@ -15030,7 +15020,7 @@
       <c r="B231" s="4" t="s">
         <v>1245</v>
       </c>
-      <c r="C231" s="11" t="s">
+      <c r="C231" s="4" t="s">
         <v>1246</v>
       </c>
       <c r="D231" s="4" t="s">
@@ -15065,7 +15055,7 @@
       <c r="B232" s="4" t="s">
         <v>1249</v>
       </c>
-      <c r="C232" s="11" t="s">
+      <c r="C232" s="4" t="s">
         <v>1250</v>
       </c>
       <c r="D232" s="4" t="s">
@@ -15100,7 +15090,7 @@
       <c r="B233" s="4" t="s">
         <v>1253</v>
       </c>
-      <c r="C233" s="11" t="s">
+      <c r="C233" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="D233" s="4" t="s">
@@ -15135,7 +15125,7 @@
       <c r="B234" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="C234" s="11" t="s">
+      <c r="C234" s="4" t="s">
         <v>1259</v>
       </c>
       <c r="D234" s="4" t="s">
@@ -15170,7 +15160,7 @@
       <c r="B235" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="C235" s="11" t="s">
+      <c r="C235" s="4" t="s">
         <v>1263</v>
       </c>
       <c r="D235" s="4" t="s">
@@ -15205,7 +15195,7 @@
       <c r="B236" s="4" t="s">
         <v>1266</v>
       </c>
-      <c r="C236" s="11" t="s">
+      <c r="C236" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="D236" s="4" t="s">
@@ -15240,7 +15230,7 @@
       <c r="B237" s="4" t="s">
         <v>1270</v>
       </c>
-      <c r="C237" s="11" t="s">
+      <c r="C237" s="4" t="s">
         <v>1271</v>
       </c>
       <c r="D237" s="4" t="s">
@@ -15275,7 +15265,7 @@
       <c r="B238" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="C238" s="11" t="s">
+      <c r="C238" s="4" t="s">
         <v>1275</v>
       </c>
       <c r="D238" s="4" t="s">
@@ -15310,7 +15300,7 @@
       <c r="B239" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="C239" s="11" t="s">
+      <c r="C239" s="4" t="s">
         <v>1279</v>
       </c>
       <c r="D239" s="4" t="s">
@@ -15345,7 +15335,7 @@
       <c r="B240" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="C240" s="11" t="s">
+      <c r="C240" s="4" t="s">
         <v>1283</v>
       </c>
       <c r="D240" s="4" t="s">
@@ -15380,7 +15370,7 @@
       <c r="B241" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="C241" s="11" t="s">
+      <c r="C241" s="4" t="s">
         <v>1287</v>
       </c>
       <c r="D241" s="4" t="s">
@@ -15415,7 +15405,7 @@
       <c r="B242" s="4" t="s">
         <v>1290</v>
       </c>
-      <c r="C242" s="11" t="s">
+      <c r="C242" s="4" t="s">
         <v>1291</v>
       </c>
       <c r="D242" s="4" t="s">
@@ -15450,7 +15440,7 @@
       <c r="B243" s="4" t="s">
         <v>1294</v>
       </c>
-      <c r="C243" s="11" t="s">
+      <c r="C243" s="4" t="s">
         <v>1295</v>
       </c>
       <c r="D243" s="4" t="s">
@@ -15485,7 +15475,7 @@
       <c r="B244" s="4" t="s">
         <v>1298</v>
       </c>
-      <c r="C244" s="11" t="s">
+      <c r="C244" s="4" t="s">
         <v>1299</v>
       </c>
       <c r="D244" s="4" t="s">
@@ -15520,7 +15510,7 @@
       <c r="B245" s="4" t="s">
         <v>1302</v>
       </c>
-      <c r="C245" s="11" t="s">
+      <c r="C245" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="D245" s="4" t="s">
@@ -15555,7 +15545,7 @@
       <c r="B246" s="4" t="s">
         <v>1306</v>
       </c>
-      <c r="C246" s="11" t="s">
+      <c r="C246" s="4" t="s">
         <v>1307</v>
       </c>
       <c r="D246" s="4" t="s">
@@ -15590,7 +15580,7 @@
       <c r="B247" s="4" t="s">
         <v>1310</v>
       </c>
-      <c r="C247" s="11" t="s">
+      <c r="C247" s="4" t="s">
         <v>1311</v>
       </c>
       <c r="D247" s="4" t="s">
@@ -15625,7 +15615,7 @@
       <c r="B248" s="4" t="s">
         <v>1314</v>
       </c>
-      <c r="C248" s="11" t="s">
+      <c r="C248" s="4" t="s">
         <v>1315</v>
       </c>
       <c r="D248" s="4" t="s">
@@ -15660,7 +15650,7 @@
       <c r="B249" s="4" t="s">
         <v>1318</v>
       </c>
-      <c r="C249" s="11" t="s">
+      <c r="C249" s="4" t="s">
         <v>1319</v>
       </c>
       <c r="D249" s="4" t="s">
@@ -15695,7 +15685,7 @@
       <c r="B250" s="4" t="s">
         <v>1322</v>
       </c>
-      <c r="C250" s="11" t="s">
+      <c r="C250" s="4" t="s">
         <v>1323</v>
       </c>
       <c r="D250" s="4" t="s">
@@ -15730,7 +15720,7 @@
       <c r="B251" s="4" t="s">
         <v>1327</v>
       </c>
-      <c r="C251" s="11" t="s">
+      <c r="C251" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="D251" s="4" t="s">
@@ -15765,7 +15755,7 @@
       <c r="B252" s="4" t="s">
         <v>1331</v>
       </c>
-      <c r="C252" s="11" t="s">
+      <c r="C252" s="4" t="s">
         <v>1332</v>
       </c>
       <c r="D252" s="4" t="s">
@@ -15800,7 +15790,7 @@
       <c r="B253" s="4" t="s">
         <v>1335</v>
       </c>
-      <c r="C253" s="11" t="s">
+      <c r="C253" s="4" t="s">
         <v>1336</v>
       </c>
       <c r="D253" s="4" t="s">
@@ -15835,7 +15825,7 @@
       <c r="B254" s="4" t="s">
         <v>1339</v>
       </c>
-      <c r="C254" s="11" t="s">
+      <c r="C254" s="4" t="s">
         <v>1340</v>
       </c>
       <c r="D254" s="4" t="s">
@@ -15870,7 +15860,7 @@
       <c r="B255" s="4" t="s">
         <v>1343</v>
       </c>
-      <c r="C255" s="11" t="s">
+      <c r="C255" s="4" t="s">
         <v>1344</v>
       </c>
       <c r="D255" s="4" t="s">
@@ -15905,7 +15895,7 @@
       <c r="B256" s="4" t="s">
         <v>1347</v>
       </c>
-      <c r="C256" s="11" t="s">
+      <c r="C256" s="4" t="s">
         <v>1348</v>
       </c>
       <c r="D256" s="4" t="s">
@@ -15940,7 +15930,7 @@
       <c r="B257" s="4" t="s">
         <v>1351</v>
       </c>
-      <c r="C257" s="11" t="s">
+      <c r="C257" s="4" t="s">
         <v>1352</v>
       </c>
       <c r="D257" s="4" t="s">
@@ -15975,7 +15965,7 @@
       <c r="B258" s="4" t="s">
         <v>1355</v>
       </c>
-      <c r="C258" s="11" t="s">
+      <c r="C258" s="4" t="s">
         <v>1356</v>
       </c>
       <c r="D258" s="4" t="s">
@@ -16010,7 +16000,7 @@
       <c r="B259" s="4" t="s">
         <v>1359</v>
       </c>
-      <c r="C259" s="11" t="s">
+      <c r="C259" s="4" t="s">
         <v>1360</v>
       </c>
       <c r="D259" s="4" t="s">
@@ -16045,7 +16035,7 @@
       <c r="B260" s="4" t="s">
         <v>1363</v>
       </c>
-      <c r="C260" s="11" t="s">
+      <c r="C260" s="4" t="s">
         <v>1364</v>
       </c>
       <c r="D260" s="4" t="s">
@@ -16080,7 +16070,7 @@
       <c r="B261" s="4" t="s">
         <v>1367</v>
       </c>
-      <c r="C261" s="11" t="s">
+      <c r="C261" s="4" t="s">
         <v>1368</v>
       </c>
       <c r="D261" s="4" t="s">
@@ -16115,7 +16105,7 @@
       <c r="B262" s="4" t="s">
         <v>1370</v>
       </c>
-      <c r="C262" s="11" t="s">
+      <c r="C262" s="4" t="s">
         <v>1371</v>
       </c>
       <c r="D262" s="4" t="s">
@@ -16150,7 +16140,7 @@
       <c r="B263" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="C263" s="11" t="s">
+      <c r="C263" s="4" t="s">
         <v>1375</v>
       </c>
       <c r="D263" s="4" t="s">
@@ -16185,7 +16175,7 @@
       <c r="B264" s="4" t="s">
         <v>1378</v>
       </c>
-      <c r="C264" s="11" t="s">
+      <c r="C264" s="4" t="s">
         <v>1379</v>
       </c>
       <c r="D264" s="4" t="s">
@@ -16220,7 +16210,7 @@
       <c r="B265" s="4" t="s">
         <v>1382</v>
       </c>
-      <c r="C265" s="11" t="s">
+      <c r="C265" s="4" t="s">
         <v>1383</v>
       </c>
       <c r="D265" s="4" t="s">
@@ -16255,7 +16245,7 @@
       <c r="B266" s="4" t="s">
         <v>1386</v>
       </c>
-      <c r="C266" s="11" t="s">
+      <c r="C266" s="4" t="s">
         <v>1387</v>
       </c>
       <c r="D266" s="4" t="s">
@@ -16290,7 +16280,7 @@
       <c r="B267" s="4" t="s">
         <v>1390</v>
       </c>
-      <c r="C267" s="11" t="s">
+      <c r="C267" s="4" t="s">
         <v>1391</v>
       </c>
       <c r="D267" s="4" t="s">
@@ -16325,7 +16315,7 @@
       <c r="B268" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="C268" s="11" t="s">
+      <c r="C268" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="D268" s="4" t="s">
@@ -16360,7 +16350,7 @@
       <c r="B269" s="4" t="s">
         <v>1398</v>
       </c>
-      <c r="C269" s="11" t="s">
+      <c r="C269" s="4" t="s">
         <v>1399</v>
       </c>
       <c r="D269" s="4" t="s">
@@ -16395,7 +16385,7 @@
       <c r="B270" s="4" t="s">
         <v>1402</v>
       </c>
-      <c r="C270" s="11" t="s">
+      <c r="C270" s="4" t="s">
         <v>1403</v>
       </c>
       <c r="D270" s="4" t="s">
@@ -16430,7 +16420,7 @@
       <c r="B271" s="4" t="s">
         <v>1407</v>
       </c>
-      <c r="C271" s="11" t="s">
+      <c r="C271" s="4" t="s">
         <v>1408</v>
       </c>
       <c r="D271" s="4" t="s">
@@ -16465,7 +16455,7 @@
       <c r="B272" s="4" t="s">
         <v>1411</v>
       </c>
-      <c r="C272" s="11" t="s">
+      <c r="C272" s="4" t="s">
         <v>1412</v>
       </c>
       <c r="D272" s="4" t="s">
@@ -16500,7 +16490,7 @@
       <c r="B273" s="4" t="s">
         <v>1415</v>
       </c>
-      <c r="C273" s="11" t="s">
+      <c r="C273" s="4" t="s">
         <v>1416</v>
       </c>
       <c r="D273" s="4" t="s">
@@ -16535,7 +16525,7 @@
       <c r="B274" s="4" t="s">
         <v>1419</v>
       </c>
-      <c r="C274" s="11" t="s">
+      <c r="C274" s="4" t="s">
         <v>1420</v>
       </c>
       <c r="D274" s="4" t="s">
@@ -16570,7 +16560,7 @@
       <c r="B275" s="4" t="s">
         <v>1423</v>
       </c>
-      <c r="C275" s="11" t="s">
+      <c r="C275" s="4" t="s">
         <v>1424</v>
       </c>
       <c r="D275" s="4" t="s">
@@ -16605,7 +16595,7 @@
       <c r="B276" s="4" t="s">
         <v>1427</v>
       </c>
-      <c r="C276" s="11" t="s">
+      <c r="C276" s="4" t="s">
         <v>1428</v>
       </c>
       <c r="D276" s="4" t="s">
@@ -16640,7 +16630,7 @@
       <c r="B277" s="4" t="s">
         <v>1431</v>
       </c>
-      <c r="C277" s="11" t="s">
+      <c r="C277" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="D277" s="4" t="s">
@@ -16675,7 +16665,7 @@
       <c r="B278" s="4" t="s">
         <v>1435</v>
       </c>
-      <c r="C278" s="11" t="s">
+      <c r="C278" s="4" t="s">
         <v>1436</v>
       </c>
       <c r="D278" s="4" t="s">
@@ -16710,7 +16700,7 @@
       <c r="B279" s="4" t="s">
         <v>1439</v>
       </c>
-      <c r="C279" s="11" t="s">
+      <c r="C279" s="4" t="s">
         <v>1440</v>
       </c>
       <c r="D279" s="4" t="s">
@@ -16745,7 +16735,7 @@
       <c r="B280" s="4" t="s">
         <v>1443</v>
       </c>
-      <c r="C280" s="11" t="s">
+      <c r="C280" s="4" t="s">
         <v>1444</v>
       </c>
       <c r="D280" s="4" t="s">
@@ -16780,7 +16770,7 @@
       <c r="B281" s="4" t="s">
         <v>1447</v>
       </c>
-      <c r="C281" s="11" t="s">
+      <c r="C281" s="4" t="s">
         <v>1448</v>
       </c>
       <c r="D281" s="4" t="s">
@@ -16815,7 +16805,7 @@
       <c r="B282" s="4" t="s">
         <v>1451</v>
       </c>
-      <c r="C282" s="11" t="s">
+      <c r="C282" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="D282" s="4" t="s">
@@ -16850,7 +16840,7 @@
       <c r="B283" s="4" t="s">
         <v>1455</v>
       </c>
-      <c r="C283" s="11" t="s">
+      <c r="C283" s="4" t="s">
         <v>1456</v>
       </c>
       <c r="D283" s="4" t="s">
@@ -16885,7 +16875,7 @@
       <c r="B284" s="4" t="s">
         <v>1459</v>
       </c>
-      <c r="C284" s="11" t="s">
+      <c r="C284" s="4" t="s">
         <v>1460</v>
       </c>
       <c r="D284" s="4" t="s">
@@ -16920,7 +16910,7 @@
       <c r="B285" s="4" t="s">
         <v>1463</v>
       </c>
-      <c r="C285" s="11" t="s">
+      <c r="C285" s="4" t="s">
         <v>1464</v>
       </c>
       <c r="D285" s="4" t="s">
@@ -16955,7 +16945,7 @@
       <c r="B286" s="4" t="s">
         <v>1467</v>
       </c>
-      <c r="C286" s="11" t="s">
+      <c r="C286" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="D286" s="4" t="s">
@@ -16990,7 +16980,7 @@
       <c r="B287" s="4" t="s">
         <v>1471</v>
       </c>
-      <c r="C287" s="11" t="s">
+      <c r="C287" s="4" t="s">
         <v>1472</v>
       </c>
       <c r="D287" s="4" t="s">
@@ -17025,7 +17015,7 @@
       <c r="B288" s="4" t="s">
         <v>1475</v>
       </c>
-      <c r="C288" s="11" t="s">
+      <c r="C288" s="4" t="s">
         <v>1476</v>
       </c>
       <c r="D288" s="4" t="s">
@@ -17060,7 +17050,7 @@
       <c r="B289" s="4" t="s">
         <v>1479</v>
       </c>
-      <c r="C289" s="11" t="s">
+      <c r="C289" s="4" t="s">
         <v>1480</v>
       </c>
       <c r="D289" s="4" t="s">
@@ -17095,7 +17085,7 @@
       <c r="B290" s="4" t="s">
         <v>1483</v>
       </c>
-      <c r="C290" s="11" t="s">
+      <c r="C290" s="4" t="s">
         <v>1484</v>
       </c>
       <c r="D290" s="4" t="s">
@@ -17130,7 +17120,7 @@
       <c r="B291" s="4" t="s">
         <v>1487</v>
       </c>
-      <c r="C291" s="11" t="s">
+      <c r="C291" s="4" t="s">
         <v>1488</v>
       </c>
       <c r="D291" s="4" t="s">
@@ -17165,7 +17155,7 @@
       <c r="B292" s="4" t="s">
         <v>1491</v>
       </c>
-      <c r="C292" s="11" t="s">
+      <c r="C292" s="4" t="s">
         <v>1492</v>
       </c>
       <c r="D292" s="4" t="s">
@@ -17200,7 +17190,7 @@
       <c r="B293" s="4" t="s">
         <v>1495</v>
       </c>
-      <c r="C293" s="11" t="s">
+      <c r="C293" s="4" t="s">
         <v>1496</v>
       </c>
       <c r="D293" s="4" t="s">
@@ -17235,7 +17225,7 @@
       <c r="B294" s="4" t="s">
         <v>1499</v>
       </c>
-      <c r="C294" s="11" t="s">
+      <c r="C294" s="4" t="s">
         <v>1500</v>
       </c>
       <c r="D294" s="4" t="s">
@@ -17270,7 +17260,7 @@
       <c r="B295" s="4" t="s">
         <v>1503</v>
       </c>
-      <c r="C295" s="11" t="s">
+      <c r="C295" s="4" t="s">
         <v>1504</v>
       </c>
       <c r="D295" s="4" t="s">
@@ -17305,7 +17295,7 @@
       <c r="B296" s="4" t="s">
         <v>1507</v>
       </c>
-      <c r="C296" s="11" t="s">
+      <c r="C296" s="4" t="s">
         <v>1508</v>
       </c>
       <c r="D296" s="4" t="s">
@@ -17340,7 +17330,7 @@
       <c r="B297" s="4" t="s">
         <v>1511</v>
       </c>
-      <c r="C297" s="11" t="s">
+      <c r="C297" s="4" t="s">
         <v>1512</v>
       </c>
       <c r="D297" s="4" t="s">
@@ -17375,7 +17365,7 @@
       <c r="B298" s="4" t="s">
         <v>1515</v>
       </c>
-      <c r="C298" s="11" t="s">
+      <c r="C298" s="4" t="s">
         <v>1516</v>
       </c>
       <c r="D298" s="4" t="s">
@@ -17410,7 +17400,7 @@
       <c r="B299" s="4" t="s">
         <v>1519</v>
       </c>
-      <c r="C299" s="11" t="s">
+      <c r="C299" s="4" t="s">
         <v>1520</v>
       </c>
       <c r="D299" s="4" t="s">
@@ -17445,7 +17435,7 @@
       <c r="B300" s="4" t="s">
         <v>1523</v>
       </c>
-      <c r="C300" s="11" t="s">
+      <c r="C300" s="4" t="s">
         <v>1524</v>
       </c>
       <c r="D300" s="4" t="s">
@@ -17480,7 +17470,7 @@
       <c r="B301" s="4" t="s">
         <v>1527</v>
       </c>
-      <c r="C301" s="11" t="s">
+      <c r="C301" s="4" t="s">
         <v>1528</v>
       </c>
       <c r="D301" s="4" t="s">
@@ -17515,7 +17505,7 @@
       <c r="B302" s="4" t="s">
         <v>1531</v>
       </c>
-      <c r="C302" s="11" t="s">
+      <c r="C302" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="D302" s="4" t="s">
@@ -17550,7 +17540,7 @@
       <c r="B303" s="4" t="s">
         <v>1535</v>
       </c>
-      <c r="C303" s="11" t="s">
+      <c r="C303" s="4" t="s">
         <v>1536</v>
       </c>
       <c r="D303" s="4" t="s">
@@ -17585,7 +17575,7 @@
       <c r="B304" s="4" t="s">
         <v>1539</v>
       </c>
-      <c r="C304" s="11" t="s">
+      <c r="C304" s="4" t="s">
         <v>1540</v>
       </c>
       <c r="D304" s="4" t="s">
@@ -17620,7 +17610,7 @@
       <c r="B305" s="4" t="s">
         <v>1543</v>
       </c>
-      <c r="C305" s="11" t="s">
+      <c r="C305" s="4" t="s">
         <v>1544</v>
       </c>
       <c r="D305" s="4" t="s">
@@ -17655,7 +17645,7 @@
       <c r="B306" s="4" t="s">
         <v>1547</v>
       </c>
-      <c r="C306" s="11" t="s">
+      <c r="C306" s="4" t="s">
         <v>1548</v>
       </c>
       <c r="D306" s="4" t="s">
@@ -17690,7 +17680,7 @@
       <c r="B307" s="4" t="s">
         <v>1551</v>
       </c>
-      <c r="C307" s="11" t="s">
+      <c r="C307" s="4" t="s">
         <v>1551</v>
       </c>
       <c r="D307" s="4" t="s">
@@ -17725,7 +17715,7 @@
       <c r="B308" s="4" t="s">
         <v>1554</v>
       </c>
-      <c r="C308" s="11" t="s">
+      <c r="C308" s="4" t="s">
         <v>1555</v>
       </c>
       <c r="D308" s="4" t="s">
@@ -17760,7 +17750,7 @@
       <c r="B309" s="4" t="s">
         <v>1558</v>
       </c>
-      <c r="C309" s="11" t="s">
+      <c r="C309" s="4" t="s">
         <v>1559</v>
       </c>
       <c r="D309" s="4" t="s">
@@ -17795,7 +17785,7 @@
       <c r="B310" s="4" t="s">
         <v>1562</v>
       </c>
-      <c r="C310" s="11" t="s">
+      <c r="C310" s="4" t="s">
         <v>1563</v>
       </c>
       <c r="D310" s="4" t="s">
@@ -17830,7 +17820,7 @@
       <c r="B311" s="4" t="s">
         <v>1566</v>
       </c>
-      <c r="C311" s="11" t="s">
+      <c r="C311" s="4" t="s">
         <v>1567</v>
       </c>
       <c r="D311" s="4" t="s">
@@ -17865,7 +17855,7 @@
       <c r="B312" s="4" t="s">
         <v>1570</v>
       </c>
-      <c r="C312" s="11" t="s">
+      <c r="C312" s="4" t="s">
         <v>1571</v>
       </c>
       <c r="D312" s="4" t="s">
@@ -17900,7 +17890,7 @@
       <c r="B313" s="4" t="s">
         <v>1574</v>
       </c>
-      <c r="C313" s="11" t="s">
+      <c r="C313" s="4" t="s">
         <v>1575</v>
       </c>
       <c r="D313" s="4" t="s">
@@ -17935,7 +17925,7 @@
       <c r="B314" s="4" t="s">
         <v>1578</v>
       </c>
-      <c r="C314" s="11" t="s">
+      <c r="C314" s="4" t="s">
         <v>1579</v>
       </c>
       <c r="D314" s="4" t="s">
@@ -17970,7 +17960,7 @@
       <c r="B315" s="4" t="s">
         <v>1582</v>
       </c>
-      <c r="C315" s="11" t="s">
+      <c r="C315" s="4" t="s">
         <v>1583</v>
       </c>
       <c r="D315" s="4" t="s">
@@ -18005,7 +17995,7 @@
       <c r="B316" s="4" t="s">
         <v>1586</v>
       </c>
-      <c r="C316" s="11" t="s">
+      <c r="C316" s="4" t="s">
         <v>1587</v>
       </c>
       <c r="D316" s="4" t="s">
@@ -18040,7 +18030,7 @@
       <c r="B317" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="C317" s="11" t="s">
+      <c r="C317" s="4" t="s">
         <v>1590</v>
       </c>
       <c r="D317" s="4" t="s">
@@ -18075,7 +18065,7 @@
       <c r="B318" s="4" t="s">
         <v>1593</v>
       </c>
-      <c r="C318" s="11" t="s">
+      <c r="C318" s="4" t="s">
         <v>1594</v>
       </c>
       <c r="D318" s="4" t="s">
@@ -18110,7 +18100,7 @@
       <c r="B319" s="4" t="s">
         <v>1597</v>
       </c>
-      <c r="C319" s="11" t="s">
+      <c r="C319" s="4" t="s">
         <v>1598</v>
       </c>
       <c r="D319" s="4" t="s">
@@ -18145,7 +18135,7 @@
       <c r="B320" s="4" t="s">
         <v>1601</v>
       </c>
-      <c r="C320" s="11" t="s">
+      <c r="C320" s="4" t="s">
         <v>1602</v>
       </c>
       <c r="D320" s="4" t="s">
@@ -18180,7 +18170,7 @@
       <c r="B321" s="4" t="s">
         <v>1605</v>
       </c>
-      <c r="C321" s="11" t="s">
+      <c r="C321" s="4" t="s">
         <v>1606</v>
       </c>
       <c r="D321" s="4" t="s">
@@ -18215,7 +18205,7 @@
       <c r="B322" s="4" t="s">
         <v>1609</v>
       </c>
-      <c r="C322" s="11" t="s">
+      <c r="C322" s="4" t="s">
         <v>1610</v>
       </c>
       <c r="D322" s="4" t="s">
@@ -18250,7 +18240,7 @@
       <c r="B323" s="4" t="s">
         <v>1613</v>
       </c>
-      <c r="C323" s="11" t="s">
+      <c r="C323" s="4" t="s">
         <v>1614</v>
       </c>
       <c r="D323" s="4" t="s">
@@ -18285,7 +18275,7 @@
       <c r="B324" s="4" t="s">
         <v>1617</v>
       </c>
-      <c r="C324" s="11" t="s">
+      <c r="C324" s="4" t="s">
         <v>1618</v>
       </c>
       <c r="D324" s="4" t="s">
@@ -18320,7 +18310,7 @@
       <c r="B325" s="4" t="s">
         <v>1621</v>
       </c>
-      <c r="C325" s="11" t="s">
+      <c r="C325" s="4" t="s">
         <v>1622</v>
       </c>
       <c r="D325" s="4" t="s">
@@ -18355,7 +18345,7 @@
       <c r="B326" s="4" t="s">
         <v>1625</v>
       </c>
-      <c r="C326" s="11" t="s">
+      <c r="C326" s="4" t="s">
         <v>1626</v>
       </c>
       <c r="D326" s="4" t="s">
@@ -18390,7 +18380,7 @@
       <c r="B327" s="4" t="s">
         <v>1629</v>
       </c>
-      <c r="C327" s="11" t="s">
+      <c r="C327" s="4" t="s">
         <v>1630</v>
       </c>
       <c r="D327" s="4" t="s">
@@ -18425,7 +18415,7 @@
       <c r="B328" s="4" t="s">
         <v>1633</v>
       </c>
-      <c r="C328" s="11" t="s">
+      <c r="C328" s="4" t="s">
         <v>1634</v>
       </c>
       <c r="D328" s="4" t="s">
@@ -18460,7 +18450,7 @@
       <c r="B329" s="4" t="s">
         <v>1637</v>
       </c>
-      <c r="C329" s="11" t="s">
+      <c r="C329" s="4" t="s">
         <v>1638</v>
       </c>
       <c r="D329" s="4" t="s">
@@ -18495,7 +18485,7 @@
       <c r="B330" s="4" t="s">
         <v>1641</v>
       </c>
-      <c r="C330" s="11" t="s">
+      <c r="C330" s="4" t="s">
         <v>1642</v>
       </c>
       <c r="D330" s="4" t="s">
@@ -18530,7 +18520,7 @@
       <c r="B331" s="4" t="s">
         <v>1645</v>
       </c>
-      <c r="C331" s="11" t="s">
+      <c r="C331" s="4" t="s">
         <v>1646</v>
       </c>
       <c r="D331" s="4" t="s">
@@ -18565,7 +18555,7 @@
       <c r="B332" s="4" t="s">
         <v>1649</v>
       </c>
-      <c r="C332" s="11" t="s">
+      <c r="C332" s="4" t="s">
         <v>1650</v>
       </c>
       <c r="D332" s="4" t="s">
@@ -18600,7 +18590,7 @@
       <c r="B333" s="4" t="s">
         <v>1653</v>
       </c>
-      <c r="C333" s="11" t="s">
+      <c r="C333" s="4" t="s">
         <v>1653</v>
       </c>
       <c r="D333" s="4" t="s">
@@ -18635,7 +18625,7 @@
       <c r="B334" s="4" t="s">
         <v>1656</v>
       </c>
-      <c r="C334" s="11" t="s">
+      <c r="C334" s="4" t="s">
         <v>1657</v>
       </c>
       <c r="D334" s="4" t="s">
@@ -18670,7 +18660,7 @@
       <c r="B335" s="4" t="s">
         <v>1660</v>
       </c>
-      <c r="C335" s="11" t="s">
+      <c r="C335" s="4" t="s">
         <v>1661</v>
       </c>
       <c r="D335" s="4" t="s">
@@ -18705,7 +18695,7 @@
       <c r="B336" s="4" t="s">
         <v>1664</v>
       </c>
-      <c r="C336" s="11" t="s">
+      <c r="C336" s="4" t="s">
         <v>1665</v>
       </c>
       <c r="D336" s="4" t="s">
@@ -18740,7 +18730,7 @@
       <c r="B337" s="4" t="s">
         <v>1668</v>
       </c>
-      <c r="C337" s="11" t="s">
+      <c r="C337" s="4" t="s">
         <v>1669</v>
       </c>
       <c r="D337" s="4" t="s">
@@ -18775,7 +18765,7 @@
       <c r="B338" s="4" t="s">
         <v>1672</v>
       </c>
-      <c r="C338" s="11" t="s">
+      <c r="C338" s="4" t="s">
         <v>1673</v>
       </c>
       <c r="D338" s="4" t="s">
@@ -18810,7 +18800,7 @@
       <c r="B339" s="4" t="s">
         <v>1676</v>
       </c>
-      <c r="C339" s="11" t="s">
+      <c r="C339" s="4" t="s">
         <v>1677</v>
       </c>
       <c r="D339" s="4" t="s">
@@ -18845,7 +18835,7 @@
       <c r="B340" s="4" t="s">
         <v>1680</v>
       </c>
-      <c r="C340" s="11" t="s">
+      <c r="C340" s="4" t="s">
         <v>1681</v>
       </c>
       <c r="D340" s="4" t="s">
@@ -18880,7 +18870,7 @@
       <c r="B341" s="4" t="s">
         <v>1684</v>
       </c>
-      <c r="C341" s="11" t="s">
+      <c r="C341" s="4" t="s">
         <v>1685</v>
       </c>
       <c r="D341" s="4" t="s">
@@ -18915,7 +18905,7 @@
       <c r="B342" s="4" t="s">
         <v>1688</v>
       </c>
-      <c r="C342" s="11" t="s">
+      <c r="C342" s="4" t="s">
         <v>1689</v>
       </c>
       <c r="D342" s="4" t="s">
@@ -18950,7 +18940,7 @@
       <c r="B343" s="4" t="s">
         <v>1692</v>
       </c>
-      <c r="C343" s="11" t="s">
+      <c r="C343" s="4" t="s">
         <v>1692</v>
       </c>
       <c r="D343" s="4" t="s">
@@ -18985,7 +18975,7 @@
       <c r="B344" s="4" t="s">
         <v>1695</v>
       </c>
-      <c r="C344" s="11" t="s">
+      <c r="C344" s="4" t="s">
         <v>1695</v>
       </c>
       <c r="D344" s="4" t="s">
@@ -19020,7 +19010,7 @@
       <c r="B345" s="4" t="s">
         <v>1698</v>
       </c>
-      <c r="C345" s="11" t="s">
+      <c r="C345" s="4" t="s">
         <v>1698</v>
       </c>
       <c r="D345" s="4" t="s">
@@ -19055,7 +19045,7 @@
       <c r="B346" s="4" t="s">
         <v>1701</v>
       </c>
-      <c r="C346" s="11" t="s">
+      <c r="C346" s="4" t="s">
         <v>1701</v>
       </c>
       <c r="D346" s="4" t="s">
@@ -19090,7 +19080,7 @@
       <c r="B347" s="4" t="s">
         <v>1704</v>
       </c>
-      <c r="C347" s="11" t="s">
+      <c r="C347" s="4" t="s">
         <v>1704</v>
       </c>
       <c r="D347" s="4" t="s">
@@ -19125,7 +19115,7 @@
       <c r="B348" s="4" t="s">
         <v>1707</v>
       </c>
-      <c r="C348" s="11" t="s">
+      <c r="C348" s="4" t="s">
         <v>1707</v>
       </c>
       <c r="D348" s="4" t="s">
@@ -19160,7 +19150,7 @@
       <c r="B349" s="4" t="s">
         <v>1710</v>
       </c>
-      <c r="C349" s="11" t="s">
+      <c r="C349" s="4" t="s">
         <v>1710</v>
       </c>
       <c r="D349" s="4" t="s">
@@ -19195,7 +19185,7 @@
       <c r="B350" s="4" t="s">
         <v>1713</v>
       </c>
-      <c r="C350" s="11" t="s">
+      <c r="C350" s="4" t="s">
         <v>1713</v>
       </c>
       <c r="D350" s="4" t="s">
@@ -19230,7 +19220,7 @@
       <c r="B351" s="4" t="s">
         <v>1716</v>
       </c>
-      <c r="C351" s="11" t="s">
+      <c r="C351" s="4" t="s">
         <v>1716</v>
       </c>
       <c r="D351" s="4" t="s">
@@ -19265,7 +19255,7 @@
       <c r="B352" s="4" t="s">
         <v>1719</v>
       </c>
-      <c r="C352" s="11" t="s">
+      <c r="C352" s="4" t="s">
         <v>1719</v>
       </c>
       <c r="D352" s="4" t="s">
@@ -19300,7 +19290,7 @@
       <c r="B353" s="4" t="s">
         <v>1722</v>
       </c>
-      <c r="C353" s="11" t="s">
+      <c r="C353" s="4" t="s">
         <v>1722</v>
       </c>
       <c r="D353" s="4" t="s">
@@ -19335,7 +19325,7 @@
       <c r="B354" s="4" t="s">
         <v>1725</v>
       </c>
-      <c r="C354" s="11" t="s">
+      <c r="C354" s="4" t="s">
         <v>1725</v>
       </c>
       <c r="D354" s="4" t="s">
@@ -19370,7 +19360,7 @@
       <c r="B355" s="4" t="s">
         <v>1728</v>
       </c>
-      <c r="C355" s="11" t="s">
+      <c r="C355" s="4" t="s">
         <v>1728</v>
       </c>
       <c r="D355" s="4" t="s">
@@ -19405,7 +19395,7 @@
       <c r="B356" s="4" t="s">
         <v>1731</v>
       </c>
-      <c r="C356" s="11" t="s">
+      <c r="C356" s="4" t="s">
         <v>1731</v>
       </c>
       <c r="D356" s="4" t="s">
@@ -19440,7 +19430,7 @@
       <c r="B357" s="4" t="s">
         <v>1734</v>
       </c>
-      <c r="C357" s="11" t="s">
+      <c r="C357" s="4" t="s">
         <v>1734</v>
       </c>
       <c r="D357" s="4" t="s">
@@ -19475,7 +19465,7 @@
       <c r="B358" s="4" t="s">
         <v>1737</v>
       </c>
-      <c r="C358" s="11" t="s">
+      <c r="C358" s="4" t="s">
         <v>1737</v>
       </c>
       <c r="D358" s="4" t="s">
@@ -19510,7 +19500,7 @@
       <c r="B359" s="4" t="s">
         <v>1740</v>
       </c>
-      <c r="C359" s="11" t="s">
+      <c r="C359" s="4" t="s">
         <v>1740</v>
       </c>
       <c r="D359" s="4" t="s">
@@ -19545,7 +19535,7 @@
       <c r="B360" s="4" t="s">
         <v>1743</v>
       </c>
-      <c r="C360" s="11" t="s">
+      <c r="C360" s="4" t="s">
         <v>1743</v>
       </c>
       <c r="D360" s="4" t="s">
@@ -19580,7 +19570,7 @@
       <c r="B361" s="4" t="s">
         <v>1746</v>
       </c>
-      <c r="C361" s="11" t="s">
+      <c r="C361" s="4" t="s">
         <v>1746</v>
       </c>
       <c r="D361" s="4" t="s">
@@ -19615,7 +19605,7 @@
       <c r="B362" s="4" t="s">
         <v>1749</v>
       </c>
-      <c r="C362" s="11" t="s">
+      <c r="C362" s="4" t="s">
         <v>1749</v>
       </c>
       <c r="D362" s="4" t="s">
@@ -19650,7 +19640,7 @@
       <c r="B363" s="4" t="s">
         <v>1752</v>
       </c>
-      <c r="C363" s="11" t="s">
+      <c r="C363" s="4" t="s">
         <v>1753</v>
       </c>
       <c r="D363" s="4" t="s">
@@ -19685,7 +19675,7 @@
       <c r="B364" s="4" t="s">
         <v>1756</v>
       </c>
-      <c r="C364" s="11" t="s">
+      <c r="C364" s="4" t="s">
         <v>1757</v>
       </c>
       <c r="D364" s="4" t="s">
@@ -19720,7 +19710,7 @@
       <c r="B365" s="4" t="s">
         <v>1760</v>
       </c>
-      <c r="C365" s="11" t="s">
+      <c r="C365" s="4" t="s">
         <v>1761</v>
       </c>
       <c r="D365" s="4" t="s">
@@ -19755,7 +19745,7 @@
       <c r="B366" s="4" t="s">
         <v>1764</v>
       </c>
-      <c r="C366" s="11" t="s">
+      <c r="C366" s="4" t="s">
         <v>1765</v>
       </c>
       <c r="D366" s="4" t="s">
@@ -19790,7 +19780,7 @@
       <c r="B367" s="4" t="s">
         <v>1768</v>
       </c>
-      <c r="C367" s="11" t="s">
+      <c r="C367" s="4" t="s">
         <v>1769</v>
       </c>
       <c r="D367" s="4" t="s">
@@ -19825,7 +19815,7 @@
       <c r="B368" s="4" t="s">
         <v>1772</v>
       </c>
-      <c r="C368" s="11" t="s">
+      <c r="C368" s="4" t="s">
         <v>1773</v>
       </c>
       <c r="D368" s="4" t="s">
@@ -19860,7 +19850,7 @@
       <c r="B369" s="4" t="s">
         <v>1776</v>
       </c>
-      <c r="C369" s="11" t="s">
+      <c r="C369" s="4" t="s">
         <v>1777</v>
       </c>
       <c r="D369" s="4" t="s">
@@ -19895,7 +19885,7 @@
       <c r="B370" s="4" t="s">
         <v>1780</v>
       </c>
-      <c r="C370" s="11" t="s">
+      <c r="C370" s="4" t="s">
         <v>1781</v>
       </c>
       <c r="D370" s="4" t="s">
@@ -19930,7 +19920,7 @@
       <c r="B371" s="4" t="s">
         <v>1784</v>
       </c>
-      <c r="C371" s="11" t="s">
+      <c r="C371" s="4" t="s">
         <v>1785</v>
       </c>
       <c r="D371" s="4" t="s">
@@ -19965,7 +19955,7 @@
       <c r="B372" s="4" t="s">
         <v>1788</v>
       </c>
-      <c r="C372" s="11" t="s">
+      <c r="C372" s="4" t="s">
         <v>1788</v>
       </c>
       <c r="D372" s="4" t="s">
@@ -20000,7 +19990,7 @@
       <c r="B373" s="4" t="s">
         <v>1791</v>
       </c>
-      <c r="C373" s="11" t="s">
+      <c r="C373" s="4" t="s">
         <v>1792</v>
       </c>
       <c r="D373" s="4" t="s">
@@ -20035,7 +20025,7 @@
       <c r="B374" s="4" t="s">
         <v>1795</v>
       </c>
-      <c r="C374" s="11" t="s">
+      <c r="C374" s="4" t="s">
         <v>1795</v>
       </c>
       <c r="D374" s="4" t="s">
@@ -20070,7 +20060,7 @@
       <c r="B375" s="4" t="s">
         <v>1798</v>
       </c>
-      <c r="C375" s="11" t="s">
+      <c r="C375" s="4" t="s">
         <v>1798</v>
       </c>
       <c r="D375" s="4" t="s">
@@ -20105,7 +20095,7 @@
       <c r="B376" s="4" t="s">
         <v>1801</v>
       </c>
-      <c r="C376" s="11" t="s">
+      <c r="C376" s="4" t="s">
         <v>1801</v>
       </c>
       <c r="D376" s="4" t="s">
@@ -20140,7 +20130,7 @@
       <c r="B377" s="4" t="s">
         <v>1804</v>
       </c>
-      <c r="C377" s="11" t="s">
+      <c r="C377" s="4" t="s">
         <v>1804</v>
       </c>
       <c r="D377" s="4" t="s">
@@ -20175,7 +20165,7 @@
       <c r="B378" s="4" t="s">
         <v>1807</v>
       </c>
-      <c r="C378" s="11" t="s">
+      <c r="C378" s="4" t="s">
         <v>1808</v>
       </c>
       <c r="D378" s="4" t="s">
@@ -20210,7 +20200,7 @@
       <c r="B379" s="4" t="s">
         <v>1811</v>
       </c>
-      <c r="C379" s="11" t="s">
+      <c r="C379" s="4" t="s">
         <v>1812</v>
       </c>
       <c r="D379" s="4" t="s">
@@ -20245,7 +20235,7 @@
       <c r="B380" s="4" t="s">
         <v>1815</v>
       </c>
-      <c r="C380" s="11" t="s">
+      <c r="C380" s="4" t="s">
         <v>1816</v>
       </c>
       <c r="D380" s="4" t="s">
@@ -20280,7 +20270,7 @@
       <c r="B381" s="4" t="s">
         <v>1819</v>
       </c>
-      <c r="C381" s="11" t="s">
+      <c r="C381" s="4" t="s">
         <v>1820</v>
       </c>
       <c r="D381" s="4" t="s">
@@ -20315,7 +20305,7 @@
       <c r="B382" s="4" t="s">
         <v>1823</v>
       </c>
-      <c r="C382" s="11" t="s">
+      <c r="C382" s="4" t="s">
         <v>1823</v>
       </c>
       <c r="D382" s="4" t="s">
@@ -20350,7 +20340,7 @@
       <c r="B383" s="4" t="s">
         <v>1826</v>
       </c>
-      <c r="C383" s="11" t="s">
+      <c r="C383" s="4" t="s">
         <v>1827</v>
       </c>
       <c r="D383" s="4" t="s">
@@ -20385,7 +20375,7 @@
       <c r="B384" s="4" t="s">
         <v>1830</v>
       </c>
-      <c r="C384" s="11" t="s">
+      <c r="C384" s="4" t="s">
         <v>1831</v>
       </c>
       <c r="D384" s="4" t="s">
@@ -20420,7 +20410,7 @@
       <c r="B385" s="4" t="s">
         <v>1834</v>
       </c>
-      <c r="C385" s="11" t="s">
+      <c r="C385" s="4" t="s">
         <v>1834</v>
       </c>
       <c r="D385" s="4" t="s">
@@ -20455,7 +20445,7 @@
       <c r="B386" s="4" t="s">
         <v>1837</v>
       </c>
-      <c r="C386" s="11" t="s">
+      <c r="C386" s="4" t="s">
         <v>1837</v>
       </c>
       <c r="D386" s="4" t="s">
@@ -20490,7 +20480,7 @@
       <c r="B387" s="4" t="s">
         <v>1840</v>
       </c>
-      <c r="C387" s="11" t="s">
+      <c r="C387" s="4" t="s">
         <v>1840</v>
       </c>
       <c r="D387" s="4" t="s">
@@ -20525,7 +20515,7 @@
       <c r="B388" s="4" t="s">
         <v>1843</v>
       </c>
-      <c r="C388" s="11" t="s">
+      <c r="C388" s="4" t="s">
         <v>1843</v>
       </c>
       <c r="D388" s="4" t="s">
@@ -20560,7 +20550,7 @@
       <c r="B389" s="4" t="s">
         <v>1846</v>
       </c>
-      <c r="C389" s="11" t="s">
+      <c r="C389" s="4" t="s">
         <v>1846</v>
       </c>
       <c r="D389" s="4" t="s">
@@ -20595,7 +20585,7 @@
       <c r="B390" s="4" t="s">
         <v>1849</v>
       </c>
-      <c r="C390" s="11" t="s">
+      <c r="C390" s="4" t="s">
         <v>1849</v>
       </c>
       <c r="D390" s="4" t="s">
@@ -20630,7 +20620,7 @@
       <c r="B391" s="4" t="s">
         <v>1852</v>
       </c>
-      <c r="C391" s="11" t="s">
+      <c r="C391" s="4" t="s">
         <v>1853</v>
       </c>
       <c r="D391" s="4" t="s">
@@ -20665,7 +20655,7 @@
       <c r="B392" s="4" t="s">
         <v>1856</v>
       </c>
-      <c r="C392" s="11" t="s">
+      <c r="C392" s="4" t="s">
         <v>1856</v>
       </c>
       <c r="D392" s="4" t="s">
@@ -20700,7 +20690,7 @@
       <c r="B393" s="4" t="s">
         <v>1859</v>
       </c>
-      <c r="C393" s="11" t="s">
+      <c r="C393" s="4" t="s">
         <v>1859</v>
       </c>
       <c r="D393" s="4" t="s">
@@ -20735,7 +20725,7 @@
       <c r="B394" s="4" t="s">
         <v>1862</v>
       </c>
-      <c r="C394" s="11" t="s">
+      <c r="C394" s="4" t="s">
         <v>1862</v>
       </c>
       <c r="D394" s="4" t="s">
@@ -20770,7 +20760,7 @@
       <c r="B395" s="4" t="s">
         <v>1865</v>
       </c>
-      <c r="C395" s="11" t="s">
+      <c r="C395" s="4" t="s">
         <v>1865</v>
       </c>
       <c r="D395" s="4" t="s">
@@ -20805,7 +20795,7 @@
       <c r="B396" s="4" t="s">
         <v>1868</v>
       </c>
-      <c r="C396" s="11" t="s">
+      <c r="C396" s="4" t="s">
         <v>1868</v>
       </c>
       <c r="D396" s="4" t="s">
@@ -20840,7 +20830,7 @@
       <c r="B397" s="4" t="s">
         <v>1871</v>
       </c>
-      <c r="C397" s="11" t="s">
+      <c r="C397" s="4" t="s">
         <v>1871</v>
       </c>
       <c r="D397" s="4" t="s">
@@ -20875,7 +20865,7 @@
       <c r="B398" s="4" t="s">
         <v>1874</v>
       </c>
-      <c r="C398" s="11" t="s">
+      <c r="C398" s="4" t="s">
         <v>1875</v>
       </c>
       <c r="D398" s="4" t="s">
@@ -20910,7 +20900,7 @@
       <c r="B399" s="4" t="s">
         <v>1878</v>
       </c>
-      <c r="C399" s="11" t="s">
+      <c r="C399" s="4" t="s">
         <v>1879</v>
       </c>
       <c r="D399" s="4" t="s">
@@ -20945,7 +20935,7 @@
       <c r="B400" s="4" t="s">
         <v>1882</v>
       </c>
-      <c r="C400" s="11" t="s">
+      <c r="C400" s="4" t="s">
         <v>1883</v>
       </c>
       <c r="D400" s="4" t="s">
@@ -20980,7 +20970,7 @@
       <c r="B401" s="4" t="s">
         <v>1886</v>
       </c>
-      <c r="C401" s="11" t="s">
+      <c r="C401" s="4" t="s">
         <v>1886</v>
       </c>
       <c r="D401" s="4" t="s">
@@ -21015,7 +21005,7 @@
       <c r="B402" s="4" t="s">
         <v>1889</v>
       </c>
-      <c r="C402" s="11" t="s">
+      <c r="C402" s="4" t="s">
         <v>1889</v>
       </c>
       <c r="D402" s="4" t="s">
@@ -21050,7 +21040,7 @@
       <c r="B403" s="4" t="s">
         <v>1892</v>
       </c>
-      <c r="C403" s="11" t="s">
+      <c r="C403" s="4" t="s">
         <v>1892</v>
       </c>
       <c r="D403" s="4" t="s">
@@ -21085,7 +21075,7 @@
       <c r="B404" s="4" t="s">
         <v>1895</v>
       </c>
-      <c r="C404" s="11" t="s">
+      <c r="C404" s="4" t="s">
         <v>1895</v>
       </c>
       <c r="D404" s="4" t="s">
@@ -21120,7 +21110,7 @@
       <c r="B405" s="4" t="s">
         <v>1898</v>
       </c>
-      <c r="C405" s="11" t="s">
+      <c r="C405" s="4" t="s">
         <v>1898</v>
       </c>
       <c r="D405" s="4" t="s">
@@ -21155,7 +21145,7 @@
       <c r="B406" s="4" t="s">
         <v>1901</v>
       </c>
-      <c r="C406" s="11" t="s">
+      <c r="C406" s="4" t="s">
         <v>1901</v>
       </c>
       <c r="D406" s="4" t="s">
@@ -21190,7 +21180,7 @@
       <c r="B407" s="4" t="s">
         <v>1904</v>
       </c>
-      <c r="C407" s="11" t="s">
+      <c r="C407" s="4" t="s">
         <v>1904</v>
       </c>
       <c r="D407" s="4" t="s">
@@ -21225,7 +21215,7 @@
       <c r="B408" s="4" t="s">
         <v>1907</v>
       </c>
-      <c r="C408" s="11" t="s">
+      <c r="C408" s="4" t="s">
         <v>1907</v>
       </c>
       <c r="D408" s="4" t="s">
@@ -21260,7 +21250,7 @@
       <c r="B409" s="4" t="s">
         <v>1910</v>
       </c>
-      <c r="C409" s="11" t="s">
+      <c r="C409" s="4" t="s">
         <v>1910</v>
       </c>
       <c r="D409" s="4" t="s">
@@ -21295,7 +21285,7 @@
       <c r="B410" s="4" t="s">
         <v>1913</v>
       </c>
-      <c r="C410" s="11" t="s">
+      <c r="C410" s="4" t="s">
         <v>1913</v>
       </c>
       <c r="D410" s="4" t="s">
@@ -21330,7 +21320,7 @@
       <c r="B411" s="4" t="s">
         <v>1916</v>
       </c>
-      <c r="C411" s="11" t="s">
+      <c r="C411" s="4" t="s">
         <v>1916</v>
       </c>
       <c r="D411" s="4" t="s">
@@ -21365,7 +21355,7 @@
       <c r="B412" s="4" t="s">
         <v>1919</v>
       </c>
-      <c r="C412" s="11" t="s">
+      <c r="C412" s="4" t="s">
         <v>1919</v>
       </c>
       <c r="D412" s="4" t="s">
@@ -21400,7 +21390,7 @@
       <c r="B413" s="4" t="s">
         <v>1922</v>
       </c>
-      <c r="C413" s="11" t="s">
+      <c r="C413" s="4" t="s">
         <v>1923</v>
       </c>
       <c r="D413" s="4" t="s">
@@ -21435,7 +21425,7 @@
       <c r="B414" s="4" t="s">
         <v>1926</v>
       </c>
-      <c r="C414" s="11" t="s">
+      <c r="C414" s="4" t="s">
         <v>1926</v>
       </c>
       <c r="D414" s="4" t="s">
@@ -21470,7 +21460,7 @@
       <c r="B415" s="4" t="s">
         <v>1929</v>
       </c>
-      <c r="C415" s="11" t="s">
+      <c r="C415" s="4" t="s">
         <v>1929</v>
       </c>
       <c r="D415" s="4" t="s">
@@ -21505,7 +21495,7 @@
       <c r="B416" s="4" t="s">
         <v>1932</v>
       </c>
-      <c r="C416" s="11" t="s">
+      <c r="C416" s="4" t="s">
         <v>1932</v>
       </c>
       <c r="D416" s="4" t="s">
@@ -21540,7 +21530,7 @@
       <c r="B417" s="4" t="s">
         <v>1935</v>
       </c>
-      <c r="C417" s="11" t="s">
+      <c r="C417" s="4" t="s">
         <v>1935</v>
       </c>
       <c r="D417" s="4" t="s">
@@ -21575,7 +21565,7 @@
       <c r="B418" s="4" t="s">
         <v>1938</v>
       </c>
-      <c r="C418" s="11" t="s">
+      <c r="C418" s="4" t="s">
         <v>1938</v>
       </c>
       <c r="D418" s="4" t="s">
@@ -21610,7 +21600,7 @@
       <c r="B419" s="4" t="s">
         <v>1941</v>
       </c>
-      <c r="C419" s="11" t="s">
+      <c r="C419" s="4" t="s">
         <v>1942</v>
       </c>
       <c r="D419" s="4" t="s">
@@ -21645,7 +21635,7 @@
       <c r="B420" s="4" t="s">
         <v>1945</v>
       </c>
-      <c r="C420" s="11" t="s">
+      <c r="C420" s="4" t="s">
         <v>1946</v>
       </c>
       <c r="D420" s="4" t="s">
@@ -21680,7 +21670,7 @@
       <c r="B421" s="4" t="s">
         <v>1949</v>
       </c>
-      <c r="C421" s="11" t="s">
+      <c r="C421" s="4" t="s">
         <v>1950</v>
       </c>
       <c r="D421" s="4" t="s">
@@ -21715,7 +21705,7 @@
       <c r="B422" s="4" t="s">
         <v>1953</v>
       </c>
-      <c r="C422" s="11" t="s">
+      <c r="C422" s="4" t="s">
         <v>1953</v>
       </c>
       <c r="D422" s="4" t="s">
@@ -21750,7 +21740,7 @@
       <c r="B423" s="4" t="s">
         <v>1956</v>
       </c>
-      <c r="C423" s="11" t="s">
+      <c r="C423" s="4" t="s">
         <v>1957</v>
       </c>
       <c r="D423" s="4" t="s">
@@ -21785,7 +21775,7 @@
       <c r="B424" s="4" t="s">
         <v>1960</v>
       </c>
-      <c r="C424" s="11" t="s">
+      <c r="C424" s="4" t="s">
         <v>1961</v>
       </c>
       <c r="D424" s="4" t="s">
@@ -21820,7 +21810,7 @@
       <c r="B425" s="4" t="s">
         <v>1964</v>
       </c>
-      <c r="C425" s="11" t="s">
+      <c r="C425" s="4" t="s">
         <v>1965</v>
       </c>
       <c r="D425" s="4" t="s">
@@ -21855,7 +21845,7 @@
       <c r="B426" s="4" t="s">
         <v>1968</v>
       </c>
-      <c r="C426" s="11" t="s">
+      <c r="C426" s="4" t="s">
         <v>1969</v>
       </c>
       <c r="D426" s="4" t="s">
@@ -21890,7 +21880,7 @@
       <c r="B427" s="4" t="s">
         <v>1972</v>
       </c>
-      <c r="C427" s="11" t="s">
+      <c r="C427" s="4" t="s">
         <v>1973</v>
       </c>
       <c r="D427" s="4" t="s">
@@ -21925,7 +21915,7 @@
       <c r="B428" s="4" t="s">
         <v>1976</v>
       </c>
-      <c r="C428" s="11" t="s">
+      <c r="C428" s="4" t="s">
         <v>1977</v>
       </c>
       <c r="D428" s="4" t="s">
@@ -21960,7 +21950,7 @@
       <c r="B429" s="4" t="s">
         <v>1980</v>
       </c>
-      <c r="C429" s="11" t="s">
+      <c r="C429" s="4" t="s">
         <v>1980</v>
       </c>
       <c r="D429" s="4" t="s">
@@ -21995,7 +21985,7 @@
       <c r="B430" s="4" t="s">
         <v>1983</v>
       </c>
-      <c r="C430" s="11" t="s">
+      <c r="C430" s="4" t="s">
         <v>1983</v>
       </c>
       <c r="D430" s="4" t="s">
@@ -22030,7 +22020,7 @@
       <c r="B431" s="4" t="s">
         <v>1986</v>
       </c>
-      <c r="C431" s="11" t="s">
+      <c r="C431" s="4" t="s">
         <v>1987</v>
       </c>
       <c r="D431" s="4" t="s">
@@ -22065,7 +22055,7 @@
       <c r="B432" s="4" t="s">
         <v>1990</v>
       </c>
-      <c r="C432" s="11" t="s">
+      <c r="C432" s="4" t="s">
         <v>1991</v>
       </c>
       <c r="D432" s="4" t="s">
@@ -22100,7 +22090,7 @@
       <c r="B433" s="4" t="s">
         <v>1994</v>
       </c>
-      <c r="C433" s="11" t="s">
+      <c r="C433" s="4" t="s">
         <v>1994</v>
       </c>
       <c r="D433" s="4" t="s">
@@ -22135,7 +22125,7 @@
       <c r="B434" s="4" t="s">
         <v>1997</v>
       </c>
-      <c r="C434" s="11" t="s">
+      <c r="C434" s="4" t="s">
         <v>1998</v>
       </c>
       <c r="D434" s="4" t="s">
@@ -22170,7 +22160,7 @@
       <c r="B435" s="4" t="s">
         <v>2001</v>
       </c>
-      <c r="C435" s="11" t="s">
+      <c r="C435" s="4" t="s">
         <v>2002</v>
       </c>
       <c r="D435" s="4" t="s">
@@ -22205,7 +22195,7 @@
       <c r="B436" s="4" t="s">
         <v>2005</v>
       </c>
-      <c r="C436" s="11" t="s">
+      <c r="C436" s="4" t="s">
         <v>2006</v>
       </c>
       <c r="D436" s="4" t="s">
@@ -22240,7 +22230,7 @@
       <c r="B437" s="4" t="s">
         <v>2009</v>
       </c>
-      <c r="C437" s="11" t="s">
+      <c r="C437" s="4" t="s">
         <v>2010</v>
       </c>
       <c r="D437" s="4" t="s">
@@ -22275,7 +22265,7 @@
       <c r="B438" s="4" t="s">
         <v>2013</v>
       </c>
-      <c r="C438" s="11" t="s">
+      <c r="C438" s="4" t="s">
         <v>2014</v>
       </c>
       <c r="D438" s="4" t="s">
@@ -22310,7 +22300,7 @@
       <c r="B439" s="4" t="s">
         <v>2017</v>
       </c>
-      <c r="C439" s="11" t="s">
+      <c r="C439" s="4" t="s">
         <v>2018</v>
       </c>
       <c r="D439" s="4" t="s">
@@ -22345,7 +22335,7 @@
       <c r="B440" s="4" t="s">
         <v>2021</v>
       </c>
-      <c r="C440" s="11" t="s">
+      <c r="C440" s="4" t="s">
         <v>2022</v>
       </c>
       <c r="D440" s="4" t="s">
@@ -22380,7 +22370,7 @@
       <c r="B441" s="4" t="s">
         <v>2025</v>
       </c>
-      <c r="C441" s="11" t="s">
+      <c r="C441" s="4" t="s">
         <v>2025</v>
       </c>
       <c r="D441" s="4" t="s">
@@ -22415,7 +22405,7 @@
       <c r="B442" s="4" t="s">
         <v>2028</v>
       </c>
-      <c r="C442" s="11" t="s">
+      <c r="C442" s="4" t="s">
         <v>2029</v>
       </c>
       <c r="D442" s="4" t="s">
@@ -22450,7 +22440,7 @@
       <c r="B443" s="4" t="s">
         <v>2032</v>
       </c>
-      <c r="C443" s="11" t="s">
+      <c r="C443" s="4" t="s">
         <v>2033</v>
       </c>
       <c r="D443" s="4" t="s">
@@ -22485,7 +22475,7 @@
       <c r="B444" s="4" t="s">
         <v>2036</v>
       </c>
-      <c r="C444" s="11" t="s">
+      <c r="C444" s="4" t="s">
         <v>2037</v>
       </c>
       <c r="D444" s="4" t="s">
@@ -22520,7 +22510,7 @@
       <c r="B445" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="C445" s="11" t="s">
+      <c r="C445" s="4" t="s">
         <v>2040</v>
       </c>
       <c r="D445" s="4" t="s">
@@ -22555,7 +22545,7 @@
       <c r="B446" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="C446" s="11" t="s">
+      <c r="C446" s="4" t="s">
         <v>2044</v>
       </c>
       <c r="D446" s="4" t="s">
@@ -22590,7 +22580,7 @@
       <c r="B447" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="C447" s="11" t="s">
+      <c r="C447" s="4" t="s">
         <v>2048</v>
       </c>
       <c r="D447" s="4" t="s">
@@ -22625,7 +22615,7 @@
       <c r="B448" s="4" t="s">
         <v>2051</v>
       </c>
-      <c r="C448" s="11" t="s">
+      <c r="C448" s="4" t="s">
         <v>2052</v>
       </c>
       <c r="D448" s="4" t="s">
@@ -22660,7 +22650,7 @@
       <c r="B449" s="4" t="s">
         <v>2055</v>
       </c>
-      <c r="C449" s="11" t="s">
+      <c r="C449" s="4" t="s">
         <v>2056</v>
       </c>
       <c r="D449" s="4" t="s">
@@ -22695,7 +22685,7 @@
       <c r="B450" s="4" t="s">
         <v>2059</v>
       </c>
-      <c r="C450" s="11" t="s">
+      <c r="C450" s="4" t="s">
         <v>2060</v>
       </c>
       <c r="D450" s="4" t="s">
@@ -22730,7 +22720,7 @@
       <c r="B451" s="4" t="s">
         <v>2063</v>
       </c>
-      <c r="C451" s="11" t="s">
+      <c r="C451" s="4" t="s">
         <v>2064</v>
       </c>
       <c r="D451" s="4" t="s">
@@ -22765,7 +22755,7 @@
       <c r="B452" s="4" t="s">
         <v>2067</v>
       </c>
-      <c r="C452" s="11" t="s">
+      <c r="C452" s="4" t="s">
         <v>2068</v>
       </c>
       <c r="D452" s="4" t="s">
